--- a/data/trending_integrated_20260915_13.xlsx
+++ b/data/trending_integrated_20260915_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6180</v>
+        <v>6310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.16%</t>
+          <t>'+29.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.54</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H2" t="n">
         <v>3.02</v>
@@ -601,7 +601,7 @@
         <v>5050</v>
       </c>
       <c r="L2" t="n">
-        <v>6250</v>
+        <v>6310</v>
       </c>
       <c r="M2" t="n">
         <v>4910</v>
@@ -610,7 +610,7 @@
         <v>3.56</v>
       </c>
       <c r="O2" t="n">
-        <v>54110977030</v>
+        <v>63056353455</v>
       </c>
       <c r="P2" t="n">
         <v>11370</v>
@@ -619,23 +619,23 @@
         <v>3300</v>
       </c>
       <c r="R2" t="n">
-        <v>-158000</v>
+        <v>-437000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>양자보안 및 스테이블코인 관련 언급. 5300원 이상에서의 마감 기대 및 5750원 입성 언급. 단주 거래 및 신용 관련 부정적 언급.</t>
+          <t>클래리티 통과 정보 유출 및 스테이블코인, 양자보안 관련 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자보안', '스테이블코인', '단주거래']</t>
+          <t>['스테이블코인', '양자보안', '클래리티']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10970</v>
+        <v>3200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.34%</t>
+          <t>'+23.79%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.06</v>
+        <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="H3" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9270</v>
+        <v>2585</v>
       </c>
       <c r="K3" t="n">
-        <v>9810</v>
+        <v>2725</v>
       </c>
       <c r="L3" t="n">
-        <v>12050</v>
+        <v>3225</v>
       </c>
       <c r="M3" t="n">
-        <v>9800</v>
+        <v>2690</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>146343071895</v>
+        <v>90292823851</v>
       </c>
       <c r="P3" t="n">
-        <v>25050</v>
+        <v>5100</v>
       </c>
       <c r="Q3" t="n">
-        <v>3705</v>
+        <v>966</v>
       </c>
       <c r="R3" t="n">
-        <v>16000</v>
+        <v>-426000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>장기지속형 주사제 관련 뉴스 및 품절주 언급. 11000원 돌파 및 2만원 목표가 설정. 조루, 털기 등 부정적 언급도 존재.</t>
+          <t>삼성과 4381억 계약 체결 및 광통신 제품 양산 준비 소식 기반 주가 급등.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주사제', '품절주', '목표가']</t>
+          <t>['삼성 계약', '광통신', '양산 준비']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25600</v>
+        <v>25700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.89%</t>
+          <t>'+17.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -794,7 +794,7 @@
         <v>4.89</v>
       </c>
       <c r="O4" t="n">
-        <v>196952847800</v>
+        <v>200655861875</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -803,23 +803,23 @@
         <v>10380</v>
       </c>
       <c r="R4" t="n">
-        <v>-76000</v>
+        <v>-1000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>프로그램 매물 감소와 정배열 기대감 속에서 주가 상승 흐름이 좋으나, 뚜렷한 공시나 뉴스는 부재함.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결 및 정배열 가는 길에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정배열', '프로그램 매물', '공시']</t>
+          <t>['삼성SDS 계약', '공급 계약', '정배열']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3000</v>
+        <v>10850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.05%</t>
+          <t>'+17.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.34</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>199</v>
+        <v>123</v>
       </c>
       <c r="H5" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2585</v>
+        <v>9270</v>
       </c>
       <c r="K5" t="n">
-        <v>2725</v>
+        <v>9810</v>
       </c>
       <c r="L5" t="n">
-        <v>3200</v>
+        <v>12050</v>
       </c>
       <c r="M5" t="n">
-        <v>2690</v>
+        <v>9800</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>80472911751</v>
+        <v>147745986565</v>
       </c>
       <c r="P5" t="n">
-        <v>5100</v>
+        <v>25050</v>
       </c>
       <c r="Q5" t="n">
-        <v>966</v>
+        <v>3705</v>
       </c>
       <c r="R5" t="n">
-        <v>-461000</v>
+        <v>-44000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성과의 4381억 계약 체결 및 광통신 제품 양산 준비 언급. 세계 최초 타이틀 및 신고가 달성 기대감.</t>
+          <t>노보노디스크 및 지투지바이오 관련 장기지속형 주사제 개발 및 세계 최초 타이틀 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['계약체결', '양산준비', '세계최초']</t>
+          <t>['장기지속형 주사제', '세계 최초', '특허']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,182 +924,182 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35650</v>
+        <v>3625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.03%</t>
+          <t>'+6.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>271</v>
+        <v>195</v>
       </c>
       <c r="H6" t="n">
-        <v>14.93</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33000</v>
+        <v>3400</v>
       </c>
       <c r="K6" t="n">
-        <v>32750</v>
+        <v>3450</v>
       </c>
       <c r="L6" t="n">
-        <v>37200</v>
+        <v>4080</v>
       </c>
       <c r="M6" t="n">
-        <v>32750</v>
+        <v>3445</v>
       </c>
       <c r="N6" t="n">
-        <v>15.06</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>46413813825</v>
+        <v>143626426642</v>
       </c>
       <c r="P6" t="n">
-        <v>50400</v>
+        <v>4335</v>
       </c>
       <c r="Q6" t="n">
-        <v>23650</v>
+        <v>1246</v>
       </c>
       <c r="R6" t="n">
-        <v>318000</v>
+        <v>120000</v>
       </c>
       <c r="S6" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
+          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저PBR', '현대제철', '상승']</t>
+          <t>['외인매수', '주가상승', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3650</v>
+        <v>50800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.35%</t>
+          <t>'+6.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="G7" t="n">
-        <v>193</v>
+        <v>523</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>13.97</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3400</v>
+        <v>47800</v>
       </c>
       <c r="K7" t="n">
-        <v>3450</v>
+        <v>47300</v>
       </c>
       <c r="L7" t="n">
-        <v>4080</v>
+        <v>54600</v>
       </c>
       <c r="M7" t="n">
-        <v>3445</v>
+        <v>46400</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>143066908754</v>
+        <v>79928923225</v>
       </c>
       <c r="P7" t="n">
-        <v>4335</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>226000</v>
+        <v>55000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
+          <t>대규모 수주 공시와 외인/기관 매수세 유입에도 불구하고 주가 변동성 확대 및 유상증자 가능성 제기. 내년 15만원 목표 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인매수', '주가상승', '대장주']</t>
+          <t>['수주', '공시', '유상증자']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51000</v>
+        <v>31950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.69%</t>
+          <t>'+5.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="G8" t="n">
-        <v>513</v>
+        <v>821</v>
       </c>
       <c r="H8" t="n">
-        <v>13.97</v>
+        <v>17.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47800</v>
+        <v>30350</v>
       </c>
       <c r="K8" t="n">
-        <v>47300</v>
+        <v>30250</v>
       </c>
       <c r="L8" t="n">
-        <v>54600</v>
+        <v>32300</v>
       </c>
       <c r="M8" t="n">
-        <v>46400</v>
+        <v>30250</v>
       </c>
       <c r="N8" t="n">
-        <v>14.15</v>
+        <v>17.55</v>
       </c>
       <c r="O8" t="n">
-        <v>78920107375</v>
+        <v>12495219775</v>
       </c>
       <c r="P8" t="n">
-        <v>108900</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>18230</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>89000</v>
+        <v>64000</v>
       </c>
       <c r="S8" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀, 대규모 수주 공시 기반 상승 기대감. 연이은 수주 소식에 따른 긍정적 전망과 함께 외인 및 기관 매수세 유입.</t>
+          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주 공시', '수소']</t>
+          <t>['FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31850</v>
+        <v>14790</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.94%</t>
+          <t>'+4.82%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>812</v>
+        <v>171</v>
       </c>
       <c r="H9" t="n">
-        <v>17.5</v>
+        <v>10.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>30350</v>
+        <v>14110</v>
       </c>
       <c r="K9" t="n">
-        <v>30250</v>
+        <v>14110</v>
       </c>
       <c r="L9" t="n">
-        <v>32300</v>
+        <v>15250</v>
       </c>
       <c r="M9" t="n">
-        <v>30250</v>
+        <v>13400</v>
       </c>
       <c r="N9" t="n">
-        <v>17.55</v>
+        <v>10.69</v>
       </c>
       <c r="O9" t="n">
-        <v>12284148825</v>
+        <v>110808921025</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>23550</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>5700</v>
       </c>
       <c r="R9" t="n">
-        <v>25000</v>
+        <v>-116000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14770</v>
+        <v>143000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.68%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>170</v>
+        <v>315</v>
       </c>
       <c r="H10" t="n">
-        <v>10.75</v>
+        <v>15.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14110</v>
+        <v>136700</v>
       </c>
       <c r="K10" t="n">
-        <v>14110</v>
+        <v>139500</v>
       </c>
       <c r="L10" t="n">
-        <v>15250</v>
+        <v>144100</v>
       </c>
       <c r="M10" t="n">
-        <v>13400</v>
+        <v>138200</v>
       </c>
       <c r="N10" t="n">
-        <v>10.69</v>
+        <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>110222707730</v>
+        <v>100478579350</v>
       </c>
       <c r="P10" t="n">
-        <v>23550</v>
+        <v>164700</v>
       </c>
       <c r="Q10" t="n">
-        <v>5700</v>
+        <v>87700</v>
       </c>
       <c r="R10" t="n">
-        <v>-68000</v>
+        <v>2000</v>
       </c>
       <c r="S10" t="n">
-        <v>87000</v>
+        <v>39000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>SK이노베이션, 합병 반대 여론 속 주가 변동성. 정유 및 배터리 업황 호조에도 합병 이슈가 하락 압력으로 작용.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['합병', '정유주']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,95 +1379,95 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>142800</v>
+        <v>17840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+3.72%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>-2.35</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="H11" t="n">
-        <v>15.81</v>
+        <v>0.35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>136700</v>
+        <v>17200</v>
       </c>
       <c r="K11" t="n">
-        <v>139500</v>
+        <v>17220</v>
       </c>
       <c r="L11" t="n">
-        <v>144100</v>
+        <v>18390</v>
       </c>
       <c r="M11" t="n">
-        <v>138200</v>
+        <v>16600</v>
       </c>
       <c r="N11" t="n">
-        <v>15.76</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>98608678100</v>
+        <v>169630027390</v>
       </c>
       <c r="P11" t="n">
-        <v>164700</v>
+        <v>30550</v>
       </c>
       <c r="Q11" t="n">
-        <v>87700</v>
+        <v>6100</v>
       </c>
       <c r="R11" t="n">
-        <v>7000</v>
+        <v>-32000</v>
       </c>
       <c r="S11" t="n">
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK이노베이션, 합병 반대 여론 속 주가 변동성. 정유 및 배터리 업황 호조에도 합병 이슈가 하락 압력으로 작용.</t>
+          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['합병', '정유주']</t>
+          <t>['양자 보안', '세계 최초', '신고가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17580</v>
+        <v>10540</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.21%</t>
+          <t>'+2.63%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2.35</v>
+        <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F12" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="G12" t="n">
-        <v>272</v>
+        <v>433</v>
       </c>
       <c r="H12" t="n">
-        <v>0.35</v>
+        <v>17.93</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17200</v>
+        <v>10270</v>
       </c>
       <c r="K12" t="n">
-        <v>17220</v>
+        <v>11000</v>
       </c>
       <c r="L12" t="n">
-        <v>18390</v>
+        <v>11650</v>
       </c>
       <c r="M12" t="n">
-        <v>16600</v>
+        <v>10010</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>166770021955</v>
+        <v>327195641010</v>
       </c>
       <c r="P12" t="n">
-        <v>30550</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>6100</v>
+        <v>1760</v>
       </c>
       <c r="R12" t="n">
-        <v>149000</v>
+        <v>139000</v>
       </c>
       <c r="S12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등에 따른 기대감. '세계최초' 타이틀 및 신고가 달성 언급. 주포 매도 및 단일가 관련 부정적 언급.</t>
+          <t>한국첨단소재의 광통신 관련 주가 급등 및 아이온큐 프라이빗 마켓 10% 상승 소식에 따른 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['양자보안', '신고가', '주포']</t>
+          <t>['광통신', '주가 급등', '아이온큐']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10470</v>
+        <v>14900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.95%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.26</v>
+        <v>-1.17</v>
       </c>
       <c r="E13" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>421</v>
+        <v>340</v>
       </c>
       <c r="H13" t="n">
-        <v>17.93</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10270</v>
+        <v>14660</v>
       </c>
       <c r="K13" t="n">
-        <v>11000</v>
+        <v>14980</v>
       </c>
       <c r="L13" t="n">
-        <v>11650</v>
+        <v>15460</v>
       </c>
       <c r="M13" t="n">
-        <v>10010</v>
+        <v>14330</v>
       </c>
       <c r="N13" t="n">
-        <v>17.67</v>
+        <v>1.17</v>
       </c>
       <c r="O13" t="n">
-        <v>323428789445</v>
+        <v>42848024095</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>36200</v>
       </c>
       <c r="Q13" t="n">
-        <v>1760</v>
+        <v>8920</v>
       </c>
       <c r="R13" t="n">
-        <v>276000</v>
+        <v>-13000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아이온큐 프리마켓 급등 및 트럼프 AI 정책 관련 기대감. 기타법인 매수 유입.</t>
+          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '아이온큐']</t>
+          <t>['유가', '이란', '외인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,169 +1660,169 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14880</v>
+        <v>18970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+1.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.17</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14660</v>
+        <v>18760</v>
       </c>
       <c r="K14" t="n">
-        <v>14980</v>
+        <v>18440</v>
       </c>
       <c r="L14" t="n">
-        <v>15460</v>
+        <v>19330</v>
       </c>
       <c r="M14" t="n">
-        <v>14330</v>
+        <v>18120</v>
       </c>
       <c r="N14" t="n">
-        <v>1.17</v>
+        <v>10.55</v>
       </c>
       <c r="O14" t="n">
-        <v>41993084255</v>
+        <v>57531165425</v>
       </c>
       <c r="P14" t="n">
-        <v>36200</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>8920</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-7000</v>
+        <v>6000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '이란', '외인']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18990</v>
+        <v>6940</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+0.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>-0.97</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>347</v>
+        <v>129</v>
       </c>
       <c r="H15" t="n">
-        <v>10.53</v>
+        <v>0.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18760</v>
+        <v>6900</v>
       </c>
       <c r="K15" t="n">
-        <v>18440</v>
+        <v>7500</v>
       </c>
       <c r="L15" t="n">
-        <v>19330</v>
+        <v>8190</v>
       </c>
       <c r="M15" t="n">
-        <v>18120</v>
+        <v>6730</v>
       </c>
       <c r="N15" t="n">
-        <v>10.55</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>56317131820</v>
+        <v>43604155800</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>10360</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>2965</v>
       </c>
       <c r="R15" t="n">
-        <v>-67000</v>
+        <v>-4000</v>
       </c>
       <c r="S15" t="n">
-        <v>-18000</v>
+        <v>1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10050</v>
+        <v>1703000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.60%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>475</v>
       </c>
       <c r="G16" t="n">
-        <v>114</v>
+        <v>2019</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6</v>
+        <v>50.27</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9990</v>
+        <v>1697000</v>
       </c>
       <c r="K16" t="n">
-        <v>10110</v>
+        <v>1690000</v>
       </c>
       <c r="L16" t="n">
-        <v>11390</v>
+        <v>1729000</v>
       </c>
       <c r="M16" t="n">
-        <v>9980</v>
+        <v>1685000</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>50.47</v>
       </c>
       <c r="O16" t="n">
-        <v>148769191565</v>
+        <v>2768857884500</v>
       </c>
       <c r="P16" t="n">
-        <v>15960</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3500</v>
+        <v>325000</v>
       </c>
       <c r="R16" t="n">
-        <v>21000</v>
+        <v>-232000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-67000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 공매도 관련 부정적 언급 다수. 신약 관련 언급 있으나 퇴출, 하한가 등의 부정적 전망 지배적.</t>
+          <t>AI 관련 기대감 속에서 기관 순매수 및 나스닥 선물 흐름에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '퇴출']</t>
+          <t>['AI', '기관 순매수', '나스닥 선물']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1707000</v>
+        <v>10020</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>94</v>
       </c>
       <c r="F17" t="n">
-        <v>476</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>2085</v>
+        <v>118</v>
       </c>
       <c r="H17" t="n">
-        <v>50.27</v>
+        <v>0.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1697000</v>
+        <v>9990</v>
       </c>
       <c r="K17" t="n">
-        <v>1690000</v>
+        <v>10110</v>
       </c>
       <c r="L17" t="n">
-        <v>1729000</v>
+        <v>11390</v>
       </c>
       <c r="M17" t="n">
-        <v>1685000</v>
+        <v>9980</v>
       </c>
       <c r="N17" t="n">
-        <v>50.47</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2694419599000</v>
+        <v>149048725725</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>15960</v>
       </c>
       <c r="Q17" t="n">
-        <v>325000</v>
+        <v>3500</v>
       </c>
       <c r="R17" t="n">
-        <v>-118000</v>
+        <v>1000</v>
       </c>
       <c r="S17" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 관련 긍정적 언급과 함께 기관 매수세 및 나스닥 선물 흐름 긍정적. 외인 매도세 및 속도 조절론 언급.</t>
+          <t>주가 조작 의혹 및 공매도 압박 속에서 신약 기대감에도 불구하고 주가 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '기관매수', '나스닥']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,130 +2028,130 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6940</v>
+        <v>249000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.58%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.97</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>491</v>
       </c>
       <c r="G18" t="n">
-        <v>128</v>
+        <v>1723</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
+        <v>46.57</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6900</v>
+        <v>249000</v>
       </c>
       <c r="K18" t="n">
-        <v>7500</v>
+        <v>248000</v>
       </c>
       <c r="L18" t="n">
-        <v>8190</v>
+        <v>252000</v>
       </c>
       <c r="M18" t="n">
-        <v>6730</v>
+        <v>247500</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>46.64</v>
       </c>
       <c r="O18" t="n">
-        <v>43343026670</v>
+        <v>1568289569750</v>
       </c>
       <c r="P18" t="n">
-        <v>10360</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>2965</v>
+        <v>75900</v>
       </c>
       <c r="R18" t="n">
-        <v>61000</v>
+        <v>-252000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>-480000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>시장 안정화 및 금리 인상 선반영 기대감 속에서 저가 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['시장 안정화', '금리 인상', '저가 매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>249500</v>
+        <v>224500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>154</v>
       </c>
       <c r="F19" t="n">
-        <v>482</v>
+        <v>78</v>
       </c>
       <c r="G19" t="n">
-        <v>1731</v>
+        <v>833</v>
       </c>
       <c r="H19" t="n">
-        <v>46.57</v>
+        <v>7.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>249000</v>
+        <v>225000</v>
       </c>
       <c r="K19" t="n">
-        <v>248000</v>
+        <v>228500</v>
       </c>
       <c r="L19" t="n">
-        <v>252000</v>
+        <v>229000</v>
       </c>
       <c r="M19" t="n">
-        <v>247500</v>
+        <v>219500</v>
       </c>
       <c r="N19" t="n">
-        <v>46.64</v>
+        <v>7.05</v>
       </c>
       <c r="O19" t="n">
-        <v>1524233520500</v>
+        <v>79585772500</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>426000</v>
       </c>
       <c r="Q19" t="n">
-        <v>75900</v>
+        <v>89500</v>
       </c>
       <c r="R19" t="n">
-        <v>-176000</v>
+        <v>-128000</v>
       </c>
       <c r="S19" t="n">
-        <v>-267000</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>시장 안정 및 금리 인상 선반영 언급. 반도체 공장 및 노조 관련 부정적 언급도 일부 존재.</t>
+          <t>머스크 테슬라의 '테라팹'에 패키징 장비 공급 뉴스 기반 주가 급등 조짐.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['시장', '금리인상', '반도체']</t>
+          <t>['테슬라', '테라팹', '패키징 장비']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>224500</v>
+        <v>8740</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>816</v>
+        <v>376</v>
       </c>
       <c r="H20" t="n">
-        <v>7.2</v>
+        <v>27.16</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>225000</v>
+        <v>8850</v>
       </c>
       <c r="K20" t="n">
-        <v>228500</v>
+        <v>8750</v>
       </c>
       <c r="L20" t="n">
-        <v>229000</v>
+        <v>8840</v>
       </c>
       <c r="M20" t="n">
-        <v>219500</v>
+        <v>8670</v>
       </c>
       <c r="N20" t="n">
-        <v>7.05</v>
+        <v>27.16</v>
       </c>
       <c r="O20" t="n">
-        <v>76927129000</v>
+        <v>17548892590</v>
       </c>
       <c r="P20" t="n">
-        <v>426000</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>89500</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>-110000</v>
+        <v>-351000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>머스크 테슬라 '테라팹' 공급 계약 소식 기반 급등 기대. 공매도 세력 언급.</t>
+          <t>대표이사 사퇴 요구 및 목표주가 하향 리포트 언급. 지속적인 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['테라팹', '공급', '공매도']</t>
+          <t>['적자', '목표주가', '리포트']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8760</v>
+        <v>14290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="H21" t="n">
-        <v>27.16</v>
+        <v>1.8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8850</v>
+        <v>14490</v>
       </c>
       <c r="K21" t="n">
-        <v>8750</v>
+        <v>14410</v>
       </c>
       <c r="L21" t="n">
-        <v>8840</v>
+        <v>14600</v>
       </c>
       <c r="M21" t="n">
-        <v>8670</v>
+        <v>13930</v>
       </c>
       <c r="N21" t="n">
-        <v>27.16</v>
+        <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>17237634310</v>
+        <v>53543850085</v>
       </c>
       <c r="P21" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q21" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R21" t="n">
-        <v>-290000</v>
+        <v>99000</v>
       </c>
       <c r="S21" t="n">
-        <v>-1000</v>
+        <v>-4000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>대표이사 사퇴 요구 및 목표주가 하향 리포트 언급. 지속적인 주가 하락에 대한 부정적 전망.</t>
+          <t>머니투데이 방송 홍보 및 15000원 돌파 기대감. 광전자와의 비교 및 광통신 섹터 전반의 관심.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['적자', '목표주가', '리포트']</t>
+          <t>['광통신', '홍보', '15000원']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,86 +2396,86 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14280</v>
+        <v>85500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>106</v>
+        <v>190</v>
       </c>
       <c r="F22" t="n">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="G22" t="n">
-        <v>448</v>
+        <v>769</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8</v>
+        <v>23.45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14490</v>
+        <v>87000</v>
       </c>
       <c r="K22" t="n">
-        <v>14410</v>
+        <v>86200</v>
       </c>
       <c r="L22" t="n">
-        <v>14600</v>
+        <v>86800</v>
       </c>
       <c r="M22" t="n">
-        <v>13930</v>
+        <v>85000</v>
       </c>
       <c r="N22" t="n">
-        <v>1.88</v>
+        <v>23.56</v>
       </c>
       <c r="O22" t="n">
-        <v>52701501545</v>
+        <v>97437181950</v>
       </c>
       <c r="P22" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q22" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R22" t="n">
-        <v>11000</v>
+        <v>-153000</v>
       </c>
       <c r="S22" t="n">
-        <v>-9000</v>
+        <v>-121000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 및 15000원 돌파 기대감. 광전자와의 비교 및 광통신 섹터 전반의 관심.</t>
+          <t>두산에너빌리티, 원전 사업 기대감 및 상승장 속 일부 신용 매수. 단기 변동성에도 긍정적 전망.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['광통신', '홍보', '15000원']</t>
+          <t>['원전', '상승장']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>85500</v>
+        <v>32500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="E23" t="n">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="F23" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>756</v>
+        <v>283</v>
       </c>
       <c r="H23" t="n">
-        <v>23.45</v>
+        <v>14.93</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,60 +2527,60 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>87000</v>
+        <v>33600</v>
       </c>
       <c r="K23" t="n">
-        <v>86200</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>86800</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>23.56</v>
+        <v>15.06</v>
       </c>
       <c r="O23" t="n">
-        <v>95136675950</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-169000</v>
+        <v>334000</v>
       </c>
       <c r="S23" t="n">
-        <v>-55000</v>
+        <v>108000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 원전 사업 기대감 및 상승장 속 일부 신용 매수. 단기 변동성에도 긍정적 전망.</t>
+          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', '상승장']</t>
+          <t>['저PBR', '현대제철', '상승']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4170</v>
+        <v>4160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-3.58%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H24" t="n">
         <v>0.77</v>
@@ -2634,7 +2634,7 @@
         <v>0.59</v>
       </c>
       <c r="O24" t="n">
-        <v>66367260290</v>
+        <v>66822793709</v>
       </c>
       <c r="P24" t="n">
         <v>8100</v>
@@ -2643,7 +2643,7 @@
         <v>592</v>
       </c>
       <c r="R24" t="n">
-        <v>39000</v>
+        <v>-112000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2694,13 +2694,13 @@
         <v>0.09</v>
       </c>
       <c r="E25" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F25" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G25" t="n">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="H25" t="n">
         <v>28.9</v>
@@ -2726,7 +2726,7 @@
         <v>28.81</v>
       </c>
       <c r="O25" t="n">
-        <v>57151967025</v>
+        <v>58434385375</v>
       </c>
       <c r="P25" t="n">
         <v>35350</v>
@@ -2735,10 +2735,10 @@
         <v>18440</v>
       </c>
       <c r="R25" t="n">
-        <v>-882000</v>
+        <v>-1538000</v>
       </c>
       <c r="S25" t="n">
-        <v>-16000</v>
+        <v>-65000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>

--- a/data/trending_integrated_20260915_13.xlsx
+++ b/data/trending_integrated_20260915_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.54</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="H2" t="n">
         <v>3.02</v>
@@ -610,7 +610,7 @@
         <v>3.56</v>
       </c>
       <c r="O2" t="n">
-        <v>63056353455</v>
+        <v>64493398665</v>
       </c>
       <c r="P2" t="n">
         <v>11370</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>클래리티 통과 정보 유출 및 스테이블코인, 양자보안 관련 기대감.</t>
+          <t>양자 보안 관련 호재 및 스테이블 코인 대장주 등극 기대감, 주가 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스테이블코인', '양자보안', '클래리티']</t>
+          <t>['양자보안', '스테이블코인', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3200</v>
+        <v>5230</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.79%</t>
+          <t>'+29.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.34</v>
+        <v>-0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34</v>
+        <v>2.68</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2585</v>
+        <v>4030</v>
       </c>
       <c r="K3" t="n">
-        <v>2725</v>
+        <v>4090</v>
       </c>
       <c r="L3" t="n">
-        <v>3225</v>
+        <v>5230</v>
       </c>
       <c r="M3" t="n">
-        <v>2690</v>
+        <v>4020</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O3" t="n">
-        <v>90292823851</v>
+        <v>48362219279</v>
       </c>
       <c r="P3" t="n">
-        <v>5100</v>
+        <v>8980</v>
       </c>
       <c r="Q3" t="n">
-        <v>966</v>
+        <v>2795</v>
       </c>
       <c r="R3" t="n">
-        <v>-426000</v>
+        <v>-185000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성과 4381억 계약 체결 및 광통신 제품 양산 준비 소식 기반 주가 급등.</t>
+          <t>11월 양자 구축 체계 의무화 및 PQC 인증, 양자 보안 대장주로서의 입지 강화.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['삼성 계약', '광통신', '양산 준비']</t>
+          <t>['양자보안', 'PQC', '의무화']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25700</v>
+        <v>3145</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.35%</t>
+          <t>'+21.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>1.34</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>21900</v>
+        <v>2585</v>
       </c>
       <c r="K4" t="n">
-        <v>21700</v>
+        <v>2725</v>
       </c>
       <c r="L4" t="n">
-        <v>26750</v>
+        <v>3295</v>
       </c>
       <c r="M4" t="n">
-        <v>21500</v>
+        <v>2690</v>
       </c>
       <c r="N4" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>200655861875</v>
+        <v>99120548724</v>
       </c>
       <c r="P4" t="n">
-        <v>50600</v>
+        <v>5100</v>
       </c>
       <c r="Q4" t="n">
-        <v>10380</v>
+        <v>966</v>
       </c>
       <c r="R4" t="n">
-        <v>-1000</v>
+        <v>-426000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급 계약 체결 및 정배열 가는 길에 따른 긍정적 전망.</t>
+          <t>삼성과 4381억 계약 체결, 광통신 제품 양산 준비 및 AI 발전 수혜 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['삼성SDS 계약', '공급 계약', '정배열']</t>
+          <t>['삼성', '광통신', 'AI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10850</v>
+        <v>11080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.04%</t>
+          <t>'+19.53%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>147745986565</v>
+        <v>150245060120</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3625</v>
+        <v>25350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.62%</t>
+          <t>'+15.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H6" t="n">
-        <v>0.83</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3400</v>
+        <v>21900</v>
       </c>
       <c r="K6" t="n">
-        <v>3450</v>
+        <v>21700</v>
       </c>
       <c r="L6" t="n">
-        <v>4080</v>
+        <v>26750</v>
       </c>
       <c r="M6" t="n">
-        <v>3445</v>
+        <v>21500</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>143626426642</v>
+        <v>203695546850</v>
       </c>
       <c r="P6" t="n">
-        <v>4335</v>
+        <v>50600</v>
       </c>
       <c r="Q6" t="n">
-        <v>1246</v>
+        <v>10380</v>
       </c>
       <c r="R6" t="n">
-        <v>120000</v>
+        <v>-1000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결 및 정배열 가는 길에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인매수', '주가상승', '대장주']</t>
+          <t>['삼성SDS 계약', '공급 계약', '정배열']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50800</v>
+        <v>35400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.28%</t>
+          <t>'+7.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>523</v>
+        <v>282</v>
       </c>
       <c r="H7" t="n">
-        <v>13.97</v>
+        <v>14.93</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>47800</v>
+        <v>33000</v>
       </c>
       <c r="K7" t="n">
-        <v>47300</v>
+        <v>32750</v>
       </c>
       <c r="L7" t="n">
-        <v>54600</v>
+        <v>37200</v>
       </c>
       <c r="M7" t="n">
-        <v>46400</v>
+        <v>32750</v>
       </c>
       <c r="N7" t="n">
-        <v>14.15</v>
+        <v>15.06</v>
       </c>
       <c r="O7" t="n">
-        <v>79928923225</v>
+        <v>48282512900</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>50400</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>23650</v>
       </c>
       <c r="R7" t="n">
-        <v>55000</v>
+        <v>334000</v>
       </c>
       <c r="S7" t="n">
-        <v>56000</v>
+        <v>108000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대규모 수주 공시와 외인/기관 매수세 유입에도 불구하고 주가 변동성 확대 및 유상증자 가능성 제기. 내년 15만원 목표 제시.</t>
+          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '공시', '유상증자']</t>
+          <t>['저PBR', '현대제철', '상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31950</v>
+        <v>3635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.27%</t>
+          <t>'+6.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="E8" t="n">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>821</v>
+        <v>197</v>
       </c>
       <c r="H8" t="n">
-        <v>17.5</v>
+        <v>0.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>30350</v>
+        <v>3400</v>
       </c>
       <c r="K8" t="n">
-        <v>30250</v>
+        <v>3450</v>
       </c>
       <c r="L8" t="n">
-        <v>32300</v>
+        <v>4080</v>
       </c>
       <c r="M8" t="n">
-        <v>30250</v>
+        <v>3445</v>
       </c>
       <c r="N8" t="n">
-        <v>17.55</v>
+        <v>0.71</v>
       </c>
       <c r="O8" t="n">
-        <v>12495219775</v>
+        <v>144070180294</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>4335</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>1246</v>
       </c>
       <c r="R8" t="n">
-        <v>64000</v>
+        <v>120000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
+          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암']</t>
+          <t>['외인매수', '주가상승', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14790</v>
+        <v>50900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.82%</t>
+          <t>'+6.49%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>-0.18</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
-        <v>171</v>
+        <v>554</v>
       </c>
       <c r="H9" t="n">
-        <v>10.75</v>
+        <v>13.97</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14110</v>
+        <v>47800</v>
       </c>
       <c r="K9" t="n">
-        <v>14110</v>
+        <v>47300</v>
       </c>
       <c r="L9" t="n">
-        <v>15250</v>
+        <v>54600</v>
       </c>
       <c r="M9" t="n">
-        <v>13400</v>
+        <v>46400</v>
       </c>
       <c r="N9" t="n">
-        <v>10.69</v>
+        <v>14.15</v>
       </c>
       <c r="O9" t="n">
-        <v>110808921025</v>
+        <v>81143771925</v>
       </c>
       <c r="P9" t="n">
-        <v>23550</v>
+        <v>108900</v>
       </c>
       <c r="Q9" t="n">
-        <v>5700</v>
+        <v>18230</v>
       </c>
       <c r="R9" t="n">
-        <v>-116000</v>
+        <v>55000</v>
       </c>
       <c r="S9" t="n">
-        <v>130000</v>
+        <v>56000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>하이퍼스케일러 및 3000억대 추가 수주 공시 확인, 20만 및 15만원 목표 주가 제시. 공매도 파산 가능성 및 적정가 35만원 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['수주 공시', '하이퍼스케일러', '적정가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,23 +1287,23 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143000</v>
+        <v>31750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1311,58 +1311,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="F10" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
-        <v>315</v>
+        <v>834</v>
       </c>
       <c r="H10" t="n">
-        <v>15.81</v>
+        <v>17.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>136700</v>
+        <v>30350</v>
       </c>
       <c r="K10" t="n">
-        <v>139500</v>
+        <v>30250</v>
       </c>
       <c r="L10" t="n">
-        <v>144100</v>
+        <v>32300</v>
       </c>
       <c r="M10" t="n">
-        <v>138200</v>
+        <v>30250</v>
       </c>
       <c r="N10" t="n">
-        <v>15.76</v>
+        <v>17.55</v>
       </c>
       <c r="O10" t="n">
-        <v>100478579350</v>
+        <v>12753985175</v>
       </c>
       <c r="P10" t="n">
-        <v>164700</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>87700</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>2000</v>
+        <v>64000</v>
       </c>
       <c r="S10" t="n">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK이노베이션, 합병 반대 여론 속 주가 변동성. 정유 및 배터리 업황 호조에도 합병 이슈가 하락 압력으로 작용.</t>
+          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['합병', '정유주']</t>
+          <t>['FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17840</v>
+        <v>14740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.72%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2.35</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="H11" t="n">
-        <v>0.35</v>
+        <v>10.75</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17200</v>
+        <v>14110</v>
       </c>
       <c r="K11" t="n">
-        <v>17220</v>
+        <v>14110</v>
       </c>
       <c r="L11" t="n">
-        <v>18390</v>
+        <v>15250</v>
       </c>
       <c r="M11" t="n">
-        <v>16600</v>
+        <v>13400</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>10.69</v>
       </c>
       <c r="O11" t="n">
-        <v>169630027390</v>
+        <v>111880551385</v>
       </c>
       <c r="P11" t="n">
-        <v>30550</v>
+        <v>23550</v>
       </c>
       <c r="Q11" t="n">
-        <v>6100</v>
+        <v>5700</v>
       </c>
       <c r="R11" t="n">
-        <v>-32000</v>
+        <v>-116000</v>
       </c>
       <c r="S11" t="n">
-        <v>3000</v>
+        <v>130000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자 보안', '세계 최초', '신고가']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10540</v>
+        <v>142600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.63%</t>
+          <t>'+4.32%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="G12" t="n">
-        <v>433</v>
+        <v>322</v>
       </c>
       <c r="H12" t="n">
-        <v>17.93</v>
+        <v>15.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10270</v>
+        <v>136700</v>
       </c>
       <c r="K12" t="n">
-        <v>11000</v>
+        <v>139500</v>
       </c>
       <c r="L12" t="n">
-        <v>11650</v>
+        <v>144100</v>
       </c>
       <c r="M12" t="n">
-        <v>10010</v>
+        <v>138200</v>
       </c>
       <c r="N12" t="n">
-        <v>17.67</v>
+        <v>15.76</v>
       </c>
       <c r="O12" t="n">
-        <v>327195641010</v>
+        <v>102302669000</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>164700</v>
       </c>
       <c r="Q12" t="n">
-        <v>1760</v>
+        <v>87700</v>
       </c>
       <c r="R12" t="n">
-        <v>139000</v>
+        <v>2000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>한국첨단소재의 광통신 관련 주가 급등 및 아이온큐 프라이빗 마켓 10% 상승 소식에 따른 기대감.</t>
+          <t>합병 반대 의견 속 정유주 슈퍼 사이클 및 배터리 사업 성장 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '주가 급등', '아이온큐']</t>
+          <t>['합병', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14900</v>
+        <v>17720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.64%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.17</v>
+        <v>-2.35</v>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G13" t="n">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14660</v>
+        <v>17200</v>
       </c>
       <c r="K13" t="n">
-        <v>14980</v>
+        <v>17220</v>
       </c>
       <c r="L13" t="n">
-        <v>15460</v>
+        <v>18390</v>
       </c>
       <c r="M13" t="n">
-        <v>14330</v>
+        <v>16600</v>
       </c>
       <c r="N13" t="n">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>42848024095</v>
+        <v>178915074330</v>
       </c>
       <c r="P13" t="n">
-        <v>36200</v>
+        <v>30550</v>
       </c>
       <c r="Q13" t="n">
-        <v>8920</v>
+        <v>6100</v>
       </c>
       <c r="R13" t="n">
-        <v>-13000</v>
+        <v>-32000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
+          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유가', '이란', '외인']</t>
+          <t>['양자 보안', '세계 최초', '신고가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,178 +1660,178 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18970</v>
+        <v>15030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.12%</t>
+          <t>'+2.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>-1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="H14" t="n">
-        <v>10.53</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18760</v>
+        <v>14660</v>
       </c>
       <c r="K14" t="n">
-        <v>18440</v>
+        <v>14980</v>
       </c>
       <c r="L14" t="n">
-        <v>19330</v>
+        <v>15460</v>
       </c>
       <c r="M14" t="n">
-        <v>18120</v>
+        <v>14330</v>
       </c>
       <c r="N14" t="n">
-        <v>10.55</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>57531165425</v>
+        <v>45314957660</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>6000</v>
+        <v>-13000</v>
       </c>
       <c r="S14" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['유가', '이란', '외인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6940</v>
+        <v>10500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.58%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.97</v>
+        <v>0.26</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
-        <v>129</v>
+        <v>426</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7</v>
+        <v>17.93</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6900</v>
+        <v>10270</v>
       </c>
       <c r="K15" t="n">
-        <v>7500</v>
+        <v>11000</v>
       </c>
       <c r="L15" t="n">
-        <v>8190</v>
+        <v>11650</v>
       </c>
       <c r="M15" t="n">
-        <v>6730</v>
+        <v>10010</v>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>17.67</v>
       </c>
       <c r="O15" t="n">
-        <v>43604155800</v>
+        <v>328841776745</v>
       </c>
       <c r="P15" t="n">
-        <v>10360</v>
+        <v>22450</v>
       </c>
       <c r="Q15" t="n">
-        <v>2965</v>
+        <v>1760</v>
       </c>
       <c r="R15" t="n">
-        <v>-4000</v>
+        <v>139000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>트럼프 AI 관련 긍정적 속보와 함께 아이온큐 급등, 기타 법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['AI', '광통신', '기타법인']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,43 +1839,43 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1703000</v>
+        <v>18940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>475</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>2019</v>
+        <v>362</v>
       </c>
       <c r="H16" t="n">
-        <v>50.27</v>
+        <v>10.53</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,183 +1883,183 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1697000</v>
+        <v>18760</v>
       </c>
       <c r="K16" t="n">
-        <v>1690000</v>
+        <v>18440</v>
       </c>
       <c r="L16" t="n">
-        <v>1729000</v>
+        <v>19330</v>
       </c>
       <c r="M16" t="n">
-        <v>1685000</v>
+        <v>18120</v>
       </c>
       <c r="N16" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2768857884500</v>
+        <v>59050010280</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-232000</v>
+        <v>6000</v>
       </c>
       <c r="S16" t="n">
-        <v>-67000</v>
+        <v>24000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 관련 기대감 속에서 기관 순매수 및 나스닥 선물 흐름에 따른 긍정적 전망.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI', '기관 순매수', '나스닥 선물']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10020</v>
+        <v>6960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+0.87%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9990</v>
+        <v>6900</v>
       </c>
       <c r="K17" t="n">
-        <v>10110</v>
+        <v>7500</v>
       </c>
       <c r="L17" t="n">
-        <v>11390</v>
+        <v>8190</v>
       </c>
       <c r="M17" t="n">
-        <v>9980</v>
+        <v>6730</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6</v>
+        <v>1.67</v>
       </c>
       <c r="O17" t="n">
-        <v>149048725725</v>
+        <v>43831753995</v>
       </c>
       <c r="P17" t="n">
-        <v>15960</v>
+        <v>10360</v>
       </c>
       <c r="Q17" t="n">
-        <v>3500</v>
+        <v>2965</v>
       </c>
       <c r="R17" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="S17" t="n">
         <v>1000</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 공매도 압박 속에서 신약 기대감에도 불구하고 주가 부진에 대한 불만.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>249000</v>
+        <v>10020</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
-        <v>491</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>1723</v>
+        <v>118</v>
       </c>
       <c r="H18" t="n">
-        <v>46.57</v>
+        <v>0.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>249000</v>
+        <v>9990</v>
       </c>
       <c r="K18" t="n">
-        <v>248000</v>
+        <v>10110</v>
       </c>
       <c r="L18" t="n">
-        <v>252000</v>
+        <v>11390</v>
       </c>
       <c r="M18" t="n">
-        <v>247500</v>
+        <v>9980</v>
       </c>
       <c r="N18" t="n">
-        <v>46.64</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1568289569750</v>
+        <v>149552199415</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q18" t="n">
-        <v>75900</v>
+        <v>3500</v>
       </c>
       <c r="R18" t="n">
-        <v>-252000</v>
+        <v>1000</v>
       </c>
       <c r="S18" t="n">
-        <v>-480000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>시장 안정화 및 금리 인상 선반영 기대감 속에서 저가 매수 기회 언급.</t>
+          <t>주가 조작 의혹 및 공매도 압박 속에서 신약 기대감에도 불구하고 주가 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['시장 안정화', '금리 인상', '저가 매수']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>224500</v>
+        <v>1698000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="E19" t="n">
-        <v>154</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="G19" t="n">
-        <v>833</v>
+        <v>1957</v>
       </c>
       <c r="H19" t="n">
-        <v>7.2</v>
+        <v>50.27</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>225000</v>
+        <v>1697000</v>
       </c>
       <c r="K19" t="n">
-        <v>228500</v>
+        <v>1690000</v>
       </c>
       <c r="L19" t="n">
-        <v>229000</v>
+        <v>1729000</v>
       </c>
       <c r="M19" t="n">
-        <v>219500</v>
+        <v>1685000</v>
       </c>
       <c r="N19" t="n">
-        <v>7.05</v>
+        <v>50.47</v>
       </c>
       <c r="O19" t="n">
-        <v>79585772500</v>
+        <v>2855159918500</v>
       </c>
       <c r="P19" t="n">
-        <v>426000</v>
+        <v>2987000</v>
       </c>
       <c r="Q19" t="n">
-        <v>89500</v>
+        <v>325000</v>
       </c>
       <c r="R19" t="n">
-        <v>-128000</v>
+        <v>-232000</v>
       </c>
       <c r="S19" t="n">
-        <v>1000</v>
+        <v>-67000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>머스크 테슬라의 '테라팹'에 패키징 장비 공급 뉴스 기반 주가 급등 조짐.</t>
+          <t>AI 관련 긍정적 전망 속에 기관 매수세 유입, 단기 조정 후 상승 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['테슬라', '테라팹', '패키징 장비']</t>
+          <t>['AI', '기관', '조정']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8740</v>
+        <v>248750</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-0.10%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>498</v>
       </c>
       <c r="G20" t="n">
-        <v>376</v>
+        <v>1658</v>
       </c>
       <c r="H20" t="n">
-        <v>27.16</v>
+        <v>46.57</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8850</v>
+        <v>249000</v>
       </c>
       <c r="K20" t="n">
-        <v>8750</v>
+        <v>248000</v>
       </c>
       <c r="L20" t="n">
-        <v>8840</v>
+        <v>252000</v>
       </c>
       <c r="M20" t="n">
-        <v>8670</v>
+        <v>247500</v>
       </c>
       <c r="N20" t="n">
-        <v>27.16</v>
+        <v>46.64</v>
       </c>
       <c r="O20" t="n">
-        <v>17548892590</v>
+        <v>1617805787000</v>
       </c>
       <c r="P20" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>8120</v>
+        <v>75900</v>
       </c>
       <c r="R20" t="n">
-        <v>-351000</v>
+        <v>-252000</v>
       </c>
       <c r="S20" t="n">
-        <v>-2000</v>
+        <v>-480000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>대표이사 사퇴 요구 및 목표주가 하향 리포트 언급. 지속적인 주가 하락에 대한 부정적 전망.</t>
+          <t>시장 안정 기대감과 함께 개미 투자 심리를 자극하는 차트 분석.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['적자', '목표주가', '리포트']</t>
+          <t>['시장', '개미', '차트']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14290</v>
+        <v>223500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.08</v>
+        <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G21" t="n">
-        <v>457</v>
+        <v>840</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14490</v>
+        <v>225000</v>
       </c>
       <c r="K21" t="n">
-        <v>14410</v>
+        <v>228500</v>
       </c>
       <c r="L21" t="n">
-        <v>14600</v>
+        <v>229000</v>
       </c>
       <c r="M21" t="n">
-        <v>13930</v>
+        <v>219500</v>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>7.05</v>
       </c>
       <c r="O21" t="n">
-        <v>53543850085</v>
+        <v>80784729750</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>426000</v>
       </c>
       <c r="Q21" t="n">
-        <v>1272</v>
+        <v>89500</v>
       </c>
       <c r="R21" t="n">
-        <v>99000</v>
+        <v>-128000</v>
       </c>
       <c r="S21" t="n">
-        <v>-4000</v>
+        <v>1000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 및 15000원 돌파 기대감. 광전자와의 비교 및 광통신 섹터 전반의 관심.</t>
+          <t>머스크 테슬라의 '테라팹'에 패키징 장비 공급 뉴스 기반 주가 급등 조짐.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['광통신', '홍보', '15000원']</t>
+          <t>['테슬라', '테라팹', '패키징 장비']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85500</v>
+        <v>8720</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.47%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="F22" t="n">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="G22" t="n">
-        <v>769</v>
+        <v>397</v>
       </c>
       <c r="H22" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K22" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L22" t="n">
-        <v>86800</v>
+        <v>8840</v>
       </c>
       <c r="M22" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N22" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O22" t="n">
-        <v>97437181950</v>
+        <v>18158513125</v>
       </c>
       <c r="P22" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q22" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R22" t="n">
-        <v>-153000</v>
+        <v>-351000</v>
       </c>
       <c r="S22" t="n">
-        <v>-121000</v>
+        <v>-2000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 원전 사업 기대감 및 상승장 속 일부 신용 매수. 단기 변동성에도 긍정적 전망.</t>
+          <t>목표주가 하향 조정 속에서도 압도적 저평가 주장, 경영진 교체 요구.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', '상승장']</t>
+          <t>['디스플레이', '목표주가', '저평가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,281 +2488,373 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32500</v>
+        <v>14220</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
-        <v>283</v>
+        <v>467</v>
       </c>
       <c r="H23" t="n">
-        <v>14.93</v>
+        <v>1.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>33600</v>
+        <v>14490</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>14410</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>13930</v>
       </c>
       <c r="N23" t="n">
-        <v>15.06</v>
+        <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>54629853980</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R23" t="n">
-        <v>334000</v>
+        <v>99000</v>
       </c>
       <c r="S23" t="n">
-        <v>108000</v>
+        <v>-4000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
+          <t>머니투데이 방송 홍보 후 주가 회복 기대감, 15000원 및 16000원 돌파 전망. 120일선 15000원 지지선 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['저PBR', '현대제철', '상승']</t>
+          <t>['광통신', '지지선', '회복']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4160</v>
+        <v>85300</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-1.95%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.18</v>
+        <v>-0.11</v>
       </c>
       <c r="E24" t="n">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="G24" t="n">
-        <v>168</v>
+        <v>792</v>
       </c>
       <c r="H24" t="n">
-        <v>0.77</v>
+        <v>23.45</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>4325</v>
+        <v>87000</v>
       </c>
       <c r="K24" t="n">
-        <v>4325</v>
+        <v>86200</v>
       </c>
       <c r="L24" t="n">
-        <v>4415</v>
+        <v>86800</v>
       </c>
       <c r="M24" t="n">
-        <v>4050</v>
+        <v>85000</v>
       </c>
       <c r="N24" t="n">
-        <v>0.59</v>
+        <v>23.56</v>
       </c>
       <c r="O24" t="n">
-        <v>66822793709</v>
+        <v>101417601450</v>
       </c>
       <c r="P24" t="n">
-        <v>8100</v>
+        <v>139200</v>
       </c>
       <c r="Q24" t="n">
-        <v>592</v>
+        <v>57000</v>
       </c>
       <c r="R24" t="n">
-        <v>-112000</v>
+        <v>-153000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-121000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
+          <t>원전 8기 관련 긍정적 전망 및 유가 상승에 따른 에너지 독립 기대감.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['공급 계약', '광전자', '매물대']</t>
+          <t>['원전', '에너지', '유가']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20900</v>
+        <v>4125</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.43%</t>
+          <t>'-4.62%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="E25" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="F25" t="n">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>441</v>
+        <v>172</v>
       </c>
       <c r="H25" t="n">
-        <v>28.9</v>
+        <v>0.77</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>22100</v>
+        <v>4325</v>
       </c>
       <c r="K25" t="n">
-        <v>21850</v>
+        <v>4325</v>
       </c>
       <c r="L25" t="n">
-        <v>21850</v>
+        <v>4415</v>
       </c>
       <c r="M25" t="n">
-        <v>20850</v>
+        <v>4050</v>
       </c>
       <c r="N25" t="n">
-        <v>28.81</v>
+        <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>58434385375</v>
+        <v>67801417877</v>
       </c>
       <c r="P25" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q25" t="n">
-        <v>18440</v>
+        <v>592</v>
       </c>
       <c r="R25" t="n">
-        <v>-1538000</v>
+        <v>-112000</v>
       </c>
       <c r="S25" t="n">
-        <v>-65000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.4조원 규모 수주 공시에도 주가 하락. 시장이 수주를 악재로 받아들이는 상황에 대한 불만 다수.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['수주', '주가하락', '공시']</t>
+          <t>['공급 계약', '광전자', '매물대']</t>
         </is>
       </c>
       <c r="X25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20850</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>'-5.66%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E26" t="n">
+        <v>185</v>
+      </c>
+      <c r="F26" t="n">
+        <v>105</v>
+      </c>
+      <c r="G26" t="n">
+        <v>446</v>
+      </c>
+      <c r="H26" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>22100</v>
+      </c>
+      <c r="K26" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L26" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20850</v>
+      </c>
+      <c r="N26" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="O26" t="n">
+        <v>58983775700</v>
+      </c>
+      <c r="P26" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-1538000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-65000</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12억 달러 규모 수주 공시에도 불구하고 주가 하락, 시장은 수주를 악재로 인식.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>['수주', '공시', '조선']</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>010140</t>
         </is>

--- a/data/trending_integrated_20260915_13.xlsx
+++ b/data/trending_integrated_20260915_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.54</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G2" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H2" t="n">
         <v>3.02</v>
@@ -610,7 +610,7 @@
         <v>3.56</v>
       </c>
       <c r="O2" t="n">
-        <v>64493398665</v>
+        <v>64716450855</v>
       </c>
       <c r="P2" t="n">
         <v>11370</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>양자 보안 관련 호재 및 스테이블 코인 대장주 등극 기대감, 주가 급등.</t>
+          <t>양자 보안 및 스테이블 코인 관련 호재로 인한 급등, 대장주 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H3" t="n">
         <v>2.68</v>
@@ -702,7 +702,7 @@
         <v>2.99</v>
       </c>
       <c r="O3" t="n">
-        <v>48362219279</v>
+        <v>48397129529</v>
       </c>
       <c r="P3" t="n">
         <v>8980</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11월 양자 구축 체계 의무화 및 PQC 인증, 양자 보안 대장주로서의 입지 강화.</t>
+          <t>11월 양자구축 체계 의무화 관련 수혜 기대, PQC·KCMVP 인증 기업으로 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', 'PQC', '의무화']</t>
+          <t>['양자보안', 'PQC', 'KCMVP']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3145</v>
+        <v>11470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.66%</t>
+          <t>'+23.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.34</v>
+        <v>-0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>219</v>
+        <v>126</v>
       </c>
       <c r="H4" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2585</v>
+        <v>9270</v>
       </c>
       <c r="K4" t="n">
-        <v>2725</v>
+        <v>9810</v>
       </c>
       <c r="L4" t="n">
-        <v>3295</v>
+        <v>12050</v>
       </c>
       <c r="M4" t="n">
-        <v>2690</v>
+        <v>9800</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>99120548724</v>
+        <v>162360584485</v>
       </c>
       <c r="P4" t="n">
-        <v>5100</v>
+        <v>25050</v>
       </c>
       <c r="Q4" t="n">
-        <v>966</v>
+        <v>3705</v>
       </c>
       <c r="R4" t="n">
-        <v>-426000</v>
+        <v>-44000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성과 4381억 계약 체결, 광통신 제품 양산 준비 및 AI 발전 수혜 기대.</t>
+          <t>노보노디스크 및 지투지바이오 관련 장기지속형 주사제 개발 및 세계 최초 타이틀 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['삼성', '광통신', 'AI']</t>
+          <t>['장기지속형 주사제', '세계 최초', '특허']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11080</v>
+        <v>3130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+19.53%</t>
+          <t>'+21.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.06</v>
+        <v>1.34</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>126</v>
+        <v>230</v>
       </c>
       <c r="H5" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9270</v>
+        <v>2585</v>
       </c>
       <c r="K5" t="n">
-        <v>9810</v>
+        <v>2725</v>
       </c>
       <c r="L5" t="n">
-        <v>12050</v>
+        <v>3295</v>
       </c>
       <c r="M5" t="n">
-        <v>9800</v>
+        <v>2690</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>150245060120</v>
+        <v>102309766786</v>
       </c>
       <c r="P5" t="n">
-        <v>25050</v>
+        <v>5100</v>
       </c>
       <c r="Q5" t="n">
-        <v>3705</v>
+        <v>966</v>
       </c>
       <c r="R5" t="n">
-        <v>-44000</v>
+        <v>-426000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>노보노디스크 및 지투지바이오 관련 장기지속형 주사제 개발 및 세계 최초 타이틀 기대감.</t>
+          <t>삼성전자 4381억 계약 체결 소식에 급등, 광통신 및 양자 보안 관련 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['장기지속형 주사제', '세계 최초', '특허']</t>
+          <t>['계약', '광통신', '양자']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25350</v>
+        <v>25300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+15.75%</t>
+          <t>'+15.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>203695546850</v>
+        <v>205886457925</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1023,175 +1023,175 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35400</v>
+        <v>3660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.27%</t>
+          <t>'+7.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="H7" t="n">
-        <v>14.93</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>33000</v>
+        <v>3400</v>
       </c>
       <c r="K7" t="n">
-        <v>32750</v>
+        <v>3450</v>
       </c>
       <c r="L7" t="n">
-        <v>37200</v>
+        <v>4080</v>
       </c>
       <c r="M7" t="n">
-        <v>32750</v>
+        <v>3445</v>
       </c>
       <c r="N7" t="n">
-        <v>15.06</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>48282512900</v>
+        <v>145172454093</v>
       </c>
       <c r="P7" t="n">
-        <v>50400</v>
+        <v>4335</v>
       </c>
       <c r="Q7" t="n">
-        <v>23650</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>334000</v>
+        <v>120000</v>
       </c>
       <c r="S7" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
+          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['저PBR', '현대제철', '상승']</t>
+          <t>['외인매수', '주가상승', '대장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3635</v>
+        <v>35300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.91%</t>
+          <t>'+6.97%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>197</v>
+        <v>292</v>
       </c>
       <c r="H8" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K8" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L8" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M8" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O8" t="n">
-        <v>144070180294</v>
+        <v>49399820250</v>
       </c>
       <c r="P8" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q8" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R8" t="n">
-        <v>120000</v>
+        <v>334000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
+          <t>현대제철은 PBR 0.22 등 저평가 지표와 함께 120일선 돌파 소식이 긍정적인 영향을 미쳤다. 한국거래소의 저PBR 기업 지원 정책에 대한 기대감과 함께 주가 상승 추세에 대한 긍정적 전망이 우세하다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인매수', '주가상승', '대장주']</t>
+          <t>['PBR', '120일선', '저평가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50900</v>
+        <v>50700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.49%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.18</v>
       </c>
       <c r="E9" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
         <v>554</v>
@@ -1254,7 +1254,7 @@
         <v>14.15</v>
       </c>
       <c r="O9" t="n">
-        <v>81143771925</v>
+        <v>82030595625</v>
       </c>
       <c r="P9" t="n">
         <v>108900</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31750</v>
+        <v>31700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+4.45%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F10" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G10" t="n">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="H10" t="n">
         <v>17.5</v>
@@ -1346,7 +1346,7 @@
         <v>17.55</v>
       </c>
       <c r="O10" t="n">
-        <v>12753985175</v>
+        <v>13058122475</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14740</v>
+        <v>142200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
-        <v>176</v>
+        <v>318</v>
       </c>
       <c r="H11" t="n">
-        <v>10.75</v>
+        <v>15.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14110</v>
+        <v>136700</v>
       </c>
       <c r="K11" t="n">
-        <v>14110</v>
+        <v>139500</v>
       </c>
       <c r="L11" t="n">
-        <v>15250</v>
+        <v>144100</v>
       </c>
       <c r="M11" t="n">
-        <v>13400</v>
+        <v>138200</v>
       </c>
       <c r="N11" t="n">
-        <v>10.69</v>
+        <v>15.76</v>
       </c>
       <c r="O11" t="n">
-        <v>111880551385</v>
+        <v>104902329300</v>
       </c>
       <c r="P11" t="n">
-        <v>23550</v>
+        <v>164700</v>
       </c>
       <c r="Q11" t="n">
-        <v>5700</v>
+        <v>87700</v>
       </c>
       <c r="R11" t="n">
-        <v>-116000</v>
+        <v>2000</v>
       </c>
       <c r="S11" t="n">
-        <v>130000</v>
+        <v>39000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>SK이노베이션 주주들은 합병 반대를 촉구하며, 회사 경영진에 대한 불만을 표출하고 있다. 주가 하락 및 변동성에 대한 우려가 나타나고 있으나, 정유주 슈퍼 사이클에 대한 기대도 일부 존재한다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['합병 반대', '주가 하락', '정유주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142600</v>
+        <v>14650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.32%</t>
+          <t>'+3.83%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>322</v>
+        <v>189</v>
       </c>
       <c r="H12" t="n">
-        <v>15.81</v>
+        <v>10.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>136700</v>
+        <v>14110</v>
       </c>
       <c r="K12" t="n">
-        <v>139500</v>
+        <v>14110</v>
       </c>
       <c r="L12" t="n">
-        <v>144100</v>
+        <v>15250</v>
       </c>
       <c r="M12" t="n">
-        <v>138200</v>
+        <v>13400</v>
       </c>
       <c r="N12" t="n">
-        <v>15.76</v>
+        <v>10.69</v>
       </c>
       <c r="O12" t="n">
-        <v>102302669000</v>
+        <v>113912718610</v>
       </c>
       <c r="P12" t="n">
-        <v>164700</v>
+        <v>23550</v>
       </c>
       <c r="Q12" t="n">
-        <v>87700</v>
+        <v>5700</v>
       </c>
       <c r="R12" t="n">
-        <v>2000</v>
+        <v>-116000</v>
       </c>
       <c r="S12" t="n">
-        <v>39000</v>
+        <v>130000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>합병 반대 의견 속 정유주 슈퍼 사이클 및 배터리 사업 성장 기대.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['합병', '정유', '배터리']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17720</v>
+        <v>15090</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.02%</t>
+          <t>'+2.93%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-2.35</v>
+        <v>-1.17</v>
       </c>
       <c r="E13" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="F13" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>289</v>
+        <v>352</v>
       </c>
       <c r="H13" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17200</v>
+        <v>14660</v>
       </c>
       <c r="K13" t="n">
-        <v>17220</v>
+        <v>14980</v>
       </c>
       <c r="L13" t="n">
-        <v>18390</v>
+        <v>15460</v>
       </c>
       <c r="M13" t="n">
-        <v>16600</v>
+        <v>14330</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>1.17</v>
       </c>
       <c r="O13" t="n">
-        <v>178915074330</v>
+        <v>50047091155</v>
       </c>
       <c r="P13" t="n">
-        <v>30550</v>
+        <v>36200</v>
       </c>
       <c r="Q13" t="n">
-        <v>6100</v>
+        <v>8920</v>
       </c>
       <c r="R13" t="n">
-        <v>-32000</v>
+        <v>-13000</v>
       </c>
       <c r="S13" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등 및 세계 최초 타이틀 기반 신고가 경신.</t>
+          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자 보안', '세계 최초', '신고가']</t>
+          <t>['유가', '이란', '외인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15030</v>
+        <v>10450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.52%</t>
+          <t>'+1.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.17</v>
+        <v>0.26</v>
       </c>
       <c r="E14" t="n">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="G14" t="n">
-        <v>343</v>
+        <v>427</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>17.93</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14660</v>
+        <v>10270</v>
       </c>
       <c r="K14" t="n">
-        <v>14980</v>
+        <v>11000</v>
       </c>
       <c r="L14" t="n">
-        <v>15460</v>
+        <v>11650</v>
       </c>
       <c r="M14" t="n">
-        <v>14330</v>
+        <v>10010</v>
       </c>
       <c r="N14" t="n">
-        <v>1.17</v>
+        <v>17.67</v>
       </c>
       <c r="O14" t="n">
-        <v>45314957660</v>
+        <v>331331118415</v>
       </c>
       <c r="P14" t="n">
-        <v>36200</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>8920</v>
+        <v>1760</v>
       </c>
       <c r="R14" t="n">
-        <v>-13000</v>
+        <v>139000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
+          <t>AI 발전 관련 기대감과 아이온큐 급등에 따른 투자 심리 개선. 기타 법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '이란', '외인']</t>
+          <t>['AI', '광통신', '아이온큐']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10500</v>
+        <v>10160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+1.70%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>426</v>
+        <v>121</v>
       </c>
       <c r="H15" t="n">
-        <v>17.93</v>
+        <v>0.6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10270</v>
+        <v>9990</v>
       </c>
       <c r="K15" t="n">
-        <v>11000</v>
+        <v>10110</v>
       </c>
       <c r="L15" t="n">
-        <v>11650</v>
+        <v>11390</v>
       </c>
       <c r="M15" t="n">
-        <v>10010</v>
+        <v>9980</v>
       </c>
       <c r="N15" t="n">
-        <v>17.67</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>328841776745</v>
+        <v>150876697155</v>
       </c>
       <c r="P15" t="n">
-        <v>22450</v>
+        <v>15960</v>
       </c>
       <c r="Q15" t="n">
-        <v>1760</v>
+        <v>3500</v>
       </c>
       <c r="R15" t="n">
-        <v>139000</v>
+        <v>1000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>트럼프 AI 관련 긍정적 속보와 함께 아이온큐 급등, 기타 법인 매수세 유입.</t>
+          <t>주가 조작 및 공매도 관련 의혹 제기, 투자자들의 불만 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '기타법인']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,169 +1844,169 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18940</v>
+        <v>17490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-2.35</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="G16" t="n">
-        <v>362</v>
+        <v>296</v>
       </c>
       <c r="H16" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18760</v>
+        <v>17200</v>
       </c>
       <c r="K16" t="n">
-        <v>18440</v>
+        <v>17220</v>
       </c>
       <c r="L16" t="n">
-        <v>19330</v>
+        <v>18390</v>
       </c>
       <c r="M16" t="n">
-        <v>18120</v>
+        <v>16600</v>
       </c>
       <c r="N16" t="n">
-        <v>10.55</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>59050010280</v>
+        <v>181467030695</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>6000</v>
+        <v>-32000</v>
       </c>
       <c r="S16" t="n">
-        <v>24000</v>
+        <v>3000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>미국 양자 보안주 폭등에 따른 동반 상승 기대, 세계 최초 타이틀 부각.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['양자보안', '세계최초', '보안주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6960</v>
+        <v>18990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.87%</t>
+          <t>'+1.23%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.97</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>131</v>
+        <v>369</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7</v>
+        <v>10.53</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6900</v>
+        <v>18760</v>
       </c>
       <c r="K17" t="n">
-        <v>7500</v>
+        <v>18440</v>
       </c>
       <c r="L17" t="n">
-        <v>8190</v>
+        <v>19330</v>
       </c>
       <c r="M17" t="n">
-        <v>6730</v>
+        <v>18120</v>
       </c>
       <c r="N17" t="n">
-        <v>1.67</v>
+        <v>10.55</v>
       </c>
       <c r="O17" t="n">
-        <v>43831753995</v>
+        <v>61054769065</v>
       </c>
       <c r="P17" t="n">
-        <v>10360</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>2965</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-4000</v>
+        <v>6000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>24000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,99 +2028,99 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10020</v>
+        <v>6930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>9990</v>
+        <v>6900</v>
       </c>
       <c r="K18" t="n">
-        <v>10110</v>
+        <v>7500</v>
       </c>
       <c r="L18" t="n">
-        <v>11390</v>
+        <v>8190</v>
       </c>
       <c r="M18" t="n">
-        <v>9980</v>
+        <v>6730</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>149552199415</v>
+        <v>44104758665</v>
       </c>
       <c r="P18" t="n">
-        <v>15960</v>
+        <v>10360</v>
       </c>
       <c r="Q18" t="n">
-        <v>3500</v>
+        <v>2965</v>
       </c>
       <c r="R18" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="S18" t="n">
         <v>1000</v>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 공매도 압박 속에서 신약 기대감에도 불구하고 주가 부진에 대한 불만.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1698000</v>
+        <v>1697000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G19" t="n">
-        <v>1957</v>
+        <v>1844</v>
       </c>
       <c r="H19" t="n">
         <v>50.27</v>
@@ -2174,7 +2174,7 @@
         <v>50.47</v>
       </c>
       <c r="O19" t="n">
-        <v>2855159918500</v>
+        <v>2965637354500</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>AI 관련 긍정적 전망 속에 기관 매수세 유입, 단기 조정 후 상승 기대.</t>
+          <t>AI 관련주로 분류되며 기관 매수세 유입, 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['AI', '기관', '조정']</t>
+          <t>['AI', '반도체', '기관']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>248750</v>
+        <v>248000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.10%</t>
+          <t>'-0.40%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G20" t="n">
-        <v>1658</v>
+        <v>1585</v>
       </c>
       <c r="H20" t="n">
         <v>46.57</v>
@@ -2266,7 +2266,7 @@
         <v>46.64</v>
       </c>
       <c r="O20" t="n">
-        <v>1617805787000</v>
+        <v>1716896973250</v>
       </c>
       <c r="P20" t="n">
         <v>374500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>시장 안정 기대감과 함께 개미 투자 심리를 자극하는 차트 분석.</t>
+          <t>시장 안정화 기대감 속 일부 투자자들의 매수 및 보유 의견. 게시판 불편함 토로.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['시장', '개미', '차트']</t>
+          <t>['시장', '반도체', '배당']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G21" t="n">
-        <v>840</v>
+        <v>891</v>
       </c>
       <c r="H21" t="n">
         <v>7.2</v>
@@ -2358,7 +2358,7 @@
         <v>7.05</v>
       </c>
       <c r="O21" t="n">
-        <v>80784729750</v>
+        <v>84880756750</v>
       </c>
       <c r="P21" t="n">
         <v>426000</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>머스크 테슬라의 '테라팹'에 패키징 장비 공급 뉴스 기반 주가 급등 조짐.</t>
+          <t>한미반도체가 일론 머스크의 테슬라 '테라팹'에 패키징 장비를 공급한다는 단독 뉴스가 있었으나, 주가 변동은 미미했다. 투자자들은 공매도 세력을 언급하며 주가 상승에 대한 기대감을 표현하고 있다.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['테슬라', '테라팹', '패키징 장비']</t>
+          <t>['패키징 장비', '테라팹', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8720</v>
+        <v>8690</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.47%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F22" t="n">
         <v>55</v>
       </c>
       <c r="G22" t="n">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="H22" t="n">
         <v>27.16</v>
@@ -2450,7 +2450,7 @@
         <v>27.16</v>
       </c>
       <c r="O22" t="n">
-        <v>18158513125</v>
+        <v>19733470605</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>목표주가 하향 조정 속에서도 압도적 저평가 주장, 경영진 교체 요구.</t>
+          <t>목표주가 하향 및 적자 지속에 대한 부정적 전망. 경영진 교체 요구.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['디스플레이', '목표주가', '저평가']</t>
+          <t>['디스플레이', '적자', '목표주가']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,79 +2495,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14220</v>
+        <v>85300</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.95%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="F23" t="n">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="G23" t="n">
-        <v>467</v>
+        <v>800</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8</v>
+        <v>23.45</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14490</v>
+        <v>87000</v>
       </c>
       <c r="K23" t="n">
-        <v>14410</v>
+        <v>86200</v>
       </c>
       <c r="L23" t="n">
-        <v>14600</v>
+        <v>86800</v>
       </c>
       <c r="M23" t="n">
-        <v>13930</v>
+        <v>85000</v>
       </c>
       <c r="N23" t="n">
-        <v>1.88</v>
+        <v>23.56</v>
       </c>
       <c r="O23" t="n">
-        <v>54629853980</v>
+        <v>105946783900</v>
       </c>
       <c r="P23" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q23" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R23" t="n">
-        <v>99000</v>
+        <v>-153000</v>
       </c>
       <c r="S23" t="n">
-        <v>-4000</v>
+        <v>-121000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 후 주가 회복 기대감, 15000원 및 16000원 돌파 전망. 120일선 15000원 지지선 언급.</t>
+          <t>두산에너빌리티는 원전 사업 관련 긍정적 언급과 함께 엑스에너지의 급등세를 기반으로 주가 상승을 기대하는 글들이 일부 있었다. 그러나 전날의 과도한 하락에 대한 언급도 존재한다.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '지지선', '회복']</t>
+          <t>['원전', '엑스에너지', '주가 상승']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2580,86 +2580,86 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>85300</v>
+        <v>14180</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E24" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="G24" t="n">
-        <v>792</v>
+        <v>471</v>
       </c>
       <c r="H24" t="n">
-        <v>23.45</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>87000</v>
+        <v>14490</v>
       </c>
       <c r="K24" t="n">
-        <v>86200</v>
+        <v>14410</v>
       </c>
       <c r="L24" t="n">
-        <v>86800</v>
+        <v>14600</v>
       </c>
       <c r="M24" t="n">
-        <v>85000</v>
+        <v>13930</v>
       </c>
       <c r="N24" t="n">
-        <v>23.56</v>
+        <v>1.88</v>
       </c>
       <c r="O24" t="n">
-        <v>101417601450</v>
+        <v>56261929725</v>
       </c>
       <c r="P24" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q24" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R24" t="n">
-        <v>-153000</v>
+        <v>99000</v>
       </c>
       <c r="S24" t="n">
-        <v>-121000</v>
+        <v>-4000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 8기 관련 긍정적 전망 및 유가 상승에 따른 에너지 독립 기대감.</t>
+          <t>머니투데이 방송 홍보 후 주가 회복 기대감, 15000원 및 16000원 돌파 전망. 120일선 15000원 지지선 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '에너지', '유가']</t>
+          <t>['광통신', '지지선', '회복']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4125</v>
+        <v>4145</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0.18</v>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G25" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>67801417877</v>
+        <v>68655234562</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20850</v>
+        <v>20800</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-5.66%</t>
+          <t>'-5.88%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F26" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G26" t="n">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2812,13 +2812,13 @@
         <v>21850</v>
       </c>
       <c r="M26" t="n">
-        <v>20850</v>
+        <v>20700</v>
       </c>
       <c r="N26" t="n">
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>58983775700</v>
+        <v>64631811200</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12억 달러 규모 수주 공시에도 불구하고 주가 하락, 시장은 수주를 악재로 인식.</t>
+          <t>12억 달러 수주 공시에도 주가 하락, 시장 반응에 대한 불만과 추가 수주 기대.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['수주', '공시', '조선']</t>
+          <t>['수주', '조선', '공시']</t>
         </is>
       </c>
       <c r="X26" t="n">

--- a/data/trending_integrated_20260915_13.xlsx
+++ b/data/trending_integrated_20260915_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6310</v>
+        <v>3150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.84%</t>
+          <t>'+58.29%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.54</v>
+        <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="H2" t="n">
-        <v>3.02</v>
+        <v>1.34</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4860</v>
+        <v>1990</v>
       </c>
       <c r="K2" t="n">
-        <v>5050</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6310</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4910</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>64716450855</v>
+        <v>104234000000</v>
       </c>
       <c r="P2" t="n">
-        <v>11370</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-437000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>양자 보안 및 스테이블 코인 관련 호재로 인한 급등, 대장주 부각.</t>
+          <t>삼성전자와의 4381억 계약 체결 및 광통신 제품 양산 준비 소식. 높은 거래량 동반 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자보안', '스테이블코인', '대장주']</t>
+          <t>['계약', '광통신', '양산']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5230</v>
+        <v>11510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.78%</t>
+          <t>'+45.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.31</v>
+        <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H3" t="n">
-        <v>2.68</v>
+        <v>1.19</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4030</v>
+        <v>7910</v>
       </c>
       <c r="K3" t="n">
-        <v>4090</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5230</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.99</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>48397129529</v>
+        <v>171834000000</v>
       </c>
       <c r="P3" t="n">
-        <v>8980</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2795</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-185000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11월 양자구축 체계 의무화 관련 수혜 기대, PQC·KCMVP 인증 기업으로 부각.</t>
+          <t>싸이모신 알파1 투여 관련 기대감과 품절주로서의 가능성 언급. 노보노디스크와의 협력 논의.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', 'PQC', 'KCMVP']</t>
+          <t>['품절주', '싸이모신', '특허']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11470</v>
+        <v>5230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.73%</t>
+          <t>'+32.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.06</v>
+        <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>1.19</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9270</v>
+        <v>3940</v>
       </c>
       <c r="K4" t="n">
-        <v>9810</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>12050</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>162360584485</v>
+        <v>48437000000</v>
       </c>
       <c r="P4" t="n">
-        <v>25050</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3705</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-44000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>노보노디스크 및 지투지바이오 관련 장기지속형 주사제 개발 및 세계 최초 타이틀 기대감.</t>
+          <t>11월 양자구축 체계 의무화에 따른 PQC, KCMVP 인증 기업으로서의 부각. 양자보안 대장주 등극 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['장기지속형 주사제', '세계 최초', '특허']</t>
+          <t>['양자보안', 'PQC', 'KCMVP']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3130</v>
+        <v>10400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.08%</t>
+          <t>'+31.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.34</v>
+        <v>0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="G5" t="n">
-        <v>230</v>
+        <v>433</v>
       </c>
       <c r="H5" t="n">
-        <v>1.34</v>
+        <v>17.93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2585</v>
+        <v>7900</v>
       </c>
       <c r="K5" t="n">
-        <v>2725</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3295</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2690</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
       <c r="O5" t="n">
-        <v>102309766786</v>
+        <v>332846000000</v>
       </c>
       <c r="P5" t="n">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>966</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-426000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자 4381억 계약 체결 소식에 급등, 광통신 및 양자 보안 관련 기대감.</t>
+          <t>아이온큐 급등과 트럼프 AI 정책 강화에 따른 광통신 대장주로서의 기대감. 기타법인 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['계약', '광통신', '양자']</t>
+          <t>['광통신', 'AI', '기타법인']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25300</v>
+        <v>6310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+15.53%</t>
+          <t>'+30.78%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>3.02</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>21900</v>
+        <v>4825</v>
       </c>
       <c r="K6" t="n">
-        <v>21700</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>26750</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.89</v>
+        <v>3.56</v>
       </c>
       <c r="O6" t="n">
-        <v>205886457925</v>
+        <v>64868000000</v>
       </c>
       <c r="P6" t="n">
-        <v>50600</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>10380</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급 계약 체결 및 정배열 가는 길에 따른 긍정적 전망.</t>
+          <t>양자 보안 및 스테이블 코인 관련 호재로 인한 급등, 대장주 부각.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['삼성SDS 계약', '공급 계약', '정배열']</t>
+          <t>['양자보안', '스테이블코인', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3660</v>
+        <v>6900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.65%</t>
+          <t>'+25.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-0.97</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,139 +1055,139 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3400</v>
+        <v>5510</v>
       </c>
       <c r="K7" t="n">
-        <v>3450</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4080</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>145172454093</v>
+        <v>44315000000</v>
       </c>
       <c r="P7" t="n">
-        <v>4335</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인매수', '주가상승', '대장주']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35300</v>
+        <v>25150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.97%</t>
+          <t>'+12.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
         <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>292</v>
+        <v>201</v>
       </c>
       <c r="H8" t="n">
-        <v>14.93</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>33000</v>
+        <v>22350</v>
       </c>
       <c r="K8" t="n">
-        <v>32750</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>37200</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>32750</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>15.06</v>
+        <v>4.89</v>
       </c>
       <c r="O8" t="n">
-        <v>49399820250</v>
+        <v>207733000000</v>
       </c>
       <c r="P8" t="n">
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>23650</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>334000</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>현대제철은 PBR 0.22 등 저평가 지표와 함께 120일선 돌파 소식이 긍정적인 영향을 미쳤다. 한국거래소의 저PBR 기업 지원 정책에 대한 기대감과 함께 주가 상승 추세에 대한 긍정적 전망이 우세하다.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결 및 정배열 가는 길에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['PBR', '120일선', '저평가']</t>
+          <t>['삼성SDS 계약', '공급 계약', '정배열']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50700</v>
+        <v>14500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+8.94%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.18</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>166</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>554</v>
+        <v>190</v>
       </c>
       <c r="H9" t="n">
-        <v>13.97</v>
+        <v>10.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>47800</v>
+        <v>13310</v>
       </c>
       <c r="K9" t="n">
-        <v>47300</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>54600</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>46400</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>14.15</v>
+        <v>10.69</v>
       </c>
       <c r="O9" t="n">
-        <v>82030595625</v>
+        <v>116185000000</v>
       </c>
       <c r="P9" t="n">
-        <v>108900</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>18230</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하이퍼스케일러 및 3000억대 추가 수주 공시 확인, 20만 및 15만원 목표 주가 제시. 공매도 파산 가능성 및 적정가 35만원 언급.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주 공시', '하이퍼스케일러', '적정가']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31700</v>
+        <v>17460</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.45%</t>
+          <t>'+8.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-2.35</v>
       </c>
       <c r="E10" t="n">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="F10" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G10" t="n">
-        <v>839</v>
+        <v>296</v>
       </c>
       <c r="H10" t="n">
-        <v>17.5</v>
+        <v>0.35</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>30350</v>
+        <v>16060</v>
       </c>
       <c r="K10" t="n">
-        <v>30250</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>32300</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>30250</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>17.55</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>13058122475</v>
+        <v>183008000000</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
+          <t>미국 양자 보안주 폭등에 따른 동반 상승 기대, 세계 최초 타이틀 부각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암']</t>
+          <t>['양자보안', '세계최초', '보안주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,222 +1384,222 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>142200</v>
+        <v>4120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+6.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="E11" t="n">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>318</v>
+        <v>162</v>
       </c>
       <c r="H11" t="n">
-        <v>15.81</v>
+        <v>0.77</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>136700</v>
+        <v>3870</v>
       </c>
       <c r="K11" t="n">
-        <v>139500</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>144100</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>138200</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>15.76</v>
+        <v>0.59</v>
       </c>
       <c r="O11" t="n">
-        <v>104902329300</v>
+        <v>69169000000</v>
       </c>
       <c r="P11" t="n">
-        <v>164700</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>87700</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK이노베이션 주주들은 합병 반대를 촉구하며, 회사 경영진에 대한 불만을 표출하고 있다. 주가 하락 및 변동성에 대한 우려가 나타나고 있으나, 정유주 슈퍼 사이클에 대한 기대도 일부 존재한다.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['합병 반대', '주가 하락', '정유주']</t>
+          <t>['공급 계약', '광전자', '매물대']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14650</v>
+        <v>15250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.83%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-1.17</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
-        <v>189</v>
+        <v>351</v>
       </c>
       <c r="H12" t="n">
-        <v>10.75</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14110</v>
+        <v>14610</v>
       </c>
       <c r="K12" t="n">
-        <v>14110</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>15250</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>13400</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>10.69</v>
+        <v>1.17</v>
       </c>
       <c r="O12" t="n">
-        <v>113912718610</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>23550</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-116000</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['유가', '이란', '외인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15090</v>
+        <v>3655</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.93%</t>
+          <t>'+3.98%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.17</v>
+        <v>0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>352</v>
+        <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14660</v>
+        <v>3515</v>
       </c>
       <c r="K13" t="n">
-        <v>14980</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>15460</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>14330</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.17</v>
+        <v>0.71</v>
       </c>
       <c r="O13" t="n">
-        <v>50047091155</v>
+        <v>146972000000</v>
       </c>
       <c r="P13" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
+          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유가', '이란', '외인']</t>
+          <t>['외인매수', '주가상승', '대장주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10450</v>
+        <v>10180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+3.67%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>427</v>
+        <v>123</v>
       </c>
       <c r="H14" t="n">
-        <v>17.93</v>
+        <v>0.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10270</v>
+        <v>9820</v>
       </c>
       <c r="K14" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11650</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>10010</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>17.67</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>331331118415</v>
+        <v>154728000000</v>
       </c>
       <c r="P14" t="n">
-        <v>22450</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1760</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>139000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>AI 발전 관련 기대감과 아이온큐 급등에 따른 투자 심리 개선. 기타 법인 매수세 유입.</t>
+          <t>주가 조작 및 공매도 관련 의혹 제기, 투자자들의 불만 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '아이온큐']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10160</v>
+        <v>14380</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.70%</t>
+          <t>'+1.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>121</v>
+        <v>475</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9990</v>
+        <v>14150</v>
       </c>
       <c r="K15" t="n">
-        <v>10110</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11390</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>9980</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>1.88</v>
       </c>
       <c r="O15" t="n">
-        <v>150876697155</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>15960</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 의혹 제기, 투자자들의 불만 표출.</t>
+          <t>머니투데이 방송 홍보 후 주가 회복 기대감, 15000원 및 16000원 돌파 전망. 120일선 15000원 지지선 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '신약']</t>
+          <t>['광통신', '지지선', '회복']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17490</v>
+        <v>226000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.69%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.35</v>
+        <v>0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="F16" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
-        <v>296</v>
+        <v>923</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35</v>
+        <v>7.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17200</v>
+        <v>231000</v>
       </c>
       <c r="K16" t="n">
-        <v>17220</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>18390</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>16600</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>7.05</v>
       </c>
       <c r="O16" t="n">
-        <v>181467030695</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-32000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등에 따른 동반 상승 기대, 세계 최초 타이틀 부각.</t>
+          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '세계최초', '보안주']</t>
+          <t>['패키징', '테라팹', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18990</v>
+        <v>8690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>369</v>
+        <v>440</v>
       </c>
       <c r="H17" t="n">
-        <v>10.53</v>
+        <v>27.16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,139 +1975,139 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18760</v>
+        <v>8900</v>
       </c>
       <c r="K17" t="n">
-        <v>18440</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>19330</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>18120</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>10.55</v>
+        <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>61054769065</v>
+        <v>20271000000</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>부진한 실적과 낮은 목표주가에 대한 불만 제기. PBR 기준 저평가 논의.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['적자', '목표주가', 'PBR']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6930</v>
+        <v>20850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'-2.57%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.97</v>
+        <v>0.09</v>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="G18" t="n">
-        <v>130</v>
+        <v>492</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
+        <v>28.9</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6900</v>
+        <v>21400</v>
       </c>
       <c r="K18" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>8190</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6730</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>28.81</v>
       </c>
       <c r="O18" t="n">
-        <v>44104758665</v>
+        <v>65866000000</v>
       </c>
       <c r="P18" t="n">
-        <v>10360</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2965</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>12억 달러 수주 공시에도 불구하고 주가 하락. 시장이 수주를 악재로 인식하는 현상 발생.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['수주', '공시', '조선']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,43 +2115,43 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1697000</v>
+        <v>32500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>475</v>
+        <v>59</v>
       </c>
       <c r="G19" t="n">
-        <v>1844</v>
+        <v>297</v>
       </c>
       <c r="H19" t="n">
-        <v>50.27</v>
+        <v>14.93</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1697000</v>
+        <v>33600</v>
       </c>
       <c r="K19" t="n">
-        <v>1690000</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1729000</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1685000</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>50.47</v>
+        <v>15.06</v>
       </c>
       <c r="O19" t="n">
-        <v>2965637354500</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>325000</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-232000</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-67000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>AI 관련주로 분류되며 기관 매수세 유입, 주가 상승 기대감 형성.</t>
+          <t>한국거래소의 저평가 기업 PBR 딱지 부착 예고에 따른 기대감. 정배열 및 120일선 돌파.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '기관']</t>
+          <t>['PBR', '저평가', '정배열']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>248000</v>
+        <v>30250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.40%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>166</v>
       </c>
       <c r="F20" t="n">
-        <v>499</v>
+        <v>107</v>
       </c>
       <c r="G20" t="n">
-        <v>1585</v>
+        <v>849</v>
       </c>
       <c r="H20" t="n">
-        <v>46.57</v>
+        <v>17.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>249000</v>
+        <v>31450</v>
       </c>
       <c r="K20" t="n">
-        <v>248000</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>252000</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>247500</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>46.64</v>
+        <v>17.55</v>
       </c>
       <c r="O20" t="n">
-        <v>1716896973250</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>75900</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-252000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-480000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>시장 안정화 기대감 속 일부 투자자들의 매수 및 보유 의견. 게시판 불편함 토로.</t>
+          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['시장', '반도체', '배당']</t>
+          <t>['FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>223500</v>
+        <v>19000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-4.47%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>891</v>
+        <v>373</v>
       </c>
       <c r="H21" t="n">
-        <v>7.2</v>
+        <v>10.53</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>225000</v>
+        <v>19890</v>
       </c>
       <c r="K21" t="n">
-        <v>228500</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>229000</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>219500</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>7.05</v>
+        <v>10.55</v>
       </c>
       <c r="O21" t="n">
-        <v>84880756750</v>
+        <v>62464000000</v>
       </c>
       <c r="P21" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>89500</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-128000</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>한미반도체가 일론 머스크의 테슬라 '테라팹'에 패키징 장비를 공급한다는 단독 뉴스가 있었으나, 주가 변동은 미미했다. 투자자들은 공매도 세력을 언급하며 주가 상승에 대한 기대감을 표현하고 있다.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['패키징 장비', '테라팹', '공매도']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8690</v>
+        <v>247500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-4.62%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>55</v>
+        <v>492</v>
       </c>
       <c r="G22" t="n">
-        <v>424</v>
+        <v>1557</v>
       </c>
       <c r="H22" t="n">
-        <v>27.16</v>
+        <v>46.57</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>8850</v>
+        <v>259500</v>
       </c>
       <c r="K22" t="n">
-        <v>8750</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>8840</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>8670</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>27.16</v>
+        <v>46.64</v>
       </c>
       <c r="O22" t="n">
-        <v>19733470605</v>
+        <v>1753772000000</v>
       </c>
       <c r="P22" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-351000</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>목표주가 하향 및 적자 지속에 대한 부정적 전망. 경영진 교체 요구.</t>
+          <t>시장 안정화 기대 속에서 금리 인상 선반영 논의. 차트 기술적 분석 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['디스플레이', '적자', '목표주가']</t>
+          <t>['시장', '금리인상', '차트']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>85300</v>
+        <v>46400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-4.92%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>-0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="F23" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="G23" t="n">
-        <v>800</v>
+        <v>561</v>
       </c>
       <c r="H23" t="n">
-        <v>23.45</v>
+        <v>13.97</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>87000</v>
+        <v>48800</v>
       </c>
       <c r="K23" t="n">
-        <v>86200</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>86800</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>23.56</v>
+        <v>14.15</v>
       </c>
       <c r="O23" t="n">
-        <v>105946783900</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-153000</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-121000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>두산에너빌리티는 원전 사업 관련 긍정적 언급과 함께 엑스에너지의 급등세를 기반으로 주가 상승을 기대하는 글들이 일부 있었다. 그러나 전날의 과도한 하락에 대한 언급도 존재한다.</t>
+          <t>하이퍼스케일러 및 3000억대 추가 수주 공시 확인, 20만 및 15만원 목표 주가 제시. 공매도 파산 가능성 및 적정가 35만원 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', '엑스에너지', '주가 상승']</t>
+          <t>['수주 공시', '하이퍼스케일러', '적정가']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,86 +2580,86 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14180</v>
+        <v>85600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-5.73%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E24" t="n">
-        <v>110</v>
+        <v>215</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="G24" t="n">
-        <v>471</v>
+        <v>815</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>23.45</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>14490</v>
+        <v>90800</v>
       </c>
       <c r="K24" t="n">
-        <v>14410</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>14600</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>13930</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.88</v>
+        <v>23.56</v>
       </c>
       <c r="O24" t="n">
-        <v>56261929725</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 후 주가 회복 기대감, 15000원 및 16000원 돌파 전망. 120일선 15000원 지지선 언급.</t>
+          <t>두산에너빌리티는 원전 사업 관련 긍정적 언급과 함께 엑스에너지의 급등세를 기반으로 주가 상승을 기대하는 글들이 일부 있었다. 그러나 전날의 과도한 하락에 대한 언급도 존재한다.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['광통신', '지지선', '회복']</t>
+          <t>['원전', '엑스에너지', '주가 상승']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2672,130 +2672,130 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4145</v>
+        <v>1693000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-6.57%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>44</v>
+        <v>480</v>
       </c>
       <c r="G25" t="n">
-        <v>174</v>
+        <v>1735</v>
       </c>
       <c r="H25" t="n">
-        <v>0.77</v>
+        <v>50.27</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4325</v>
+        <v>1812000</v>
       </c>
       <c r="K25" t="n">
-        <v>4325</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>4415</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4050</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.59</v>
+        <v>50.47</v>
       </c>
       <c r="O25" t="n">
-        <v>68655234562</v>
+        <v>3036938000000</v>
       </c>
       <c r="P25" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-112000</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
+          <t>AI 관련 기술 발전 속도와 금리 인상 영향에 대한 논의. 기관 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['공급 계약', '광전자', '매물대']</t>
+          <t>['AI', '금리', '기관']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20800</v>
+        <v>133900</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-7.53%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="E26" t="n">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="F26" t="n">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="G26" t="n">
-        <v>467</v>
+        <v>319</v>
       </c>
       <c r="H26" t="n">
-        <v>28.9</v>
+        <v>15.81</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,51 +2803,51 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>22100</v>
+        <v>144800</v>
       </c>
       <c r="K26" t="n">
-        <v>21850</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>21850</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>20700</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>28.81</v>
+        <v>15.76</v>
       </c>
       <c r="O26" t="n">
-        <v>64631811200</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>35350</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>18440</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-1538000</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-65000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 주가 하락, 시장 반응에 대한 불만과 추가 수주 기대.</t>
+          <t>SK이노베이션 주주들은 합병 반대를 촉구하며, 회사 경영진에 대한 불만을 표출하고 있다. 주가 하락 및 변동성에 대한 우려가 나타나고 있으나, 정유주 슈퍼 사이클에 대한 기대도 일부 존재한다.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['수주', '조선', '공시']</t>
+          <t>['합병 반대', '주가 하락', '정유주']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>096770</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260915_13.xlsx
+++ b/data/trending_integrated_20260915_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3150</v>
+        <v>6310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+58.29%</t>
+          <t>'+29.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.34</v>
+        <v>-0.54</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
-        <v>1.34</v>
+        <v>3.02</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1990</v>
+        <v>4860</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5050</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6310</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4910</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O2" t="n">
-        <v>104234000000</v>
+        <v>65219092835</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>11370</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-437000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성전자와의 4381억 계약 체결 및 광통신 제품 양산 준비 소식. 높은 거래량 동반 급등.</t>
+          <t>양자 보안 및 스테이블 코인 관련 호재로 인한 급등, 대장주 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['계약', '광통신', '양산']</t>
+          <t>['양자보안', '스테이블코인', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11510</v>
+        <v>5230</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+45.51%</t>
+          <t>'+29.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.06</v>
+        <v>-0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
-        <v>1.19</v>
+        <v>2.68</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7910</v>
+        <v>4030</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4090</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5230</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4020</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>2.99</v>
       </c>
       <c r="O3" t="n">
-        <v>171834000000</v>
+        <v>48532910789</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>8980</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2795</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-185000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>싸이모신 알파1 투여 관련 기대감과 품절주로서의 가능성 언급. 노보노디스크와의 협력 논의.</t>
+          <t>11월 양자구축 체계 의무화에 따른 PQC, KCMVP 인증 기업으로서의 부각. 양자보안 대장주 등극 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['품절주', '싸이모신', '특허']</t>
+          <t>['양자보안', 'PQC', 'KCMVP']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5230</v>
+        <v>3220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+32.74%</t>
+          <t>'+24.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.31</v>
+        <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="H4" t="n">
-        <v>2.68</v>
+        <v>1.34</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3940</v>
+        <v>2585</v>
       </c>
       <c r="K4" t="n">
+        <v>2725</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3295</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2690</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.99</v>
-      </c>
       <c r="O4" t="n">
-        <v>48437000000</v>
+        <v>107256380200</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>966</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-426000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>11월 양자구축 체계 의무화에 따른 PQC, KCMVP 인증 기업으로서의 부각. 양자보안 대장주 등극 기대.</t>
+          <t>삼성과의 대규모 계약 체결 사실 언급. 광통신 및 양자 관련 테마주로 부각되며 급등 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자보안', 'PQC', 'KCMVP']</t>
+          <t>['계약체결', '광통신', '양자']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10400</v>
+        <v>11220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+31.65%</t>
+          <t>'+21.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.26</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>433</v>
+        <v>142</v>
       </c>
       <c r="H5" t="n">
-        <v>17.93</v>
+        <v>1.19</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7900</v>
+        <v>9270</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9810</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>12050</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="N5" t="n">
-        <v>17.67</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>332846000000</v>
+        <v>176998231570</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>25050</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3705</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-44000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>아이온큐 급등과 트럼프 AI 정책 강화에 따른 광통신 대장주로서의 기대감. 기타법인 매수세 유입 확인.</t>
+          <t>신규 파이프라인 및 특허 기반의 고가 목표 제시. "세계 최초" 타이틀 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '기타법인']</t>
+          <t>['신규파이프라인', '특허', '세계최초']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6310</v>
+        <v>25050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+30.78%</t>
+          <t>'+14.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.54</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="H6" t="n">
-        <v>3.02</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4825</v>
+        <v>21900</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>26750</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="N6" t="n">
-        <v>3.56</v>
+        <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>64868000000</v>
+        <v>208901538275</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>50600</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>10380</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>양자 보안 및 스테이블 코인 관련 호재로 인한 급등, 대장주 부각.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결 및 정배열 가는 길에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자보안', '스테이블코인', '대장주']</t>
+          <t>['삼성SDS 계약', '공급 계약', '정배열']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,183 +1011,183 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6900</v>
+        <v>35400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+25.23%</t>
+          <t>'+7.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.97</v>
+        <v>-0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>130</v>
+        <v>299</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>14.93</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5510</v>
+        <v>33000</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>32750</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>37200</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>32750</v>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>15.06</v>
       </c>
       <c r="O7" t="n">
-        <v>44315000000</v>
+        <v>51128651950</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>50400</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>23650</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>334000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['PBR', '저평가', '정배열']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25150</v>
+        <v>51000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+12.53%</t>
+          <t>'+6.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="G8" t="n">
-        <v>201</v>
+        <v>582</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>13.97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>22350</v>
+        <v>47800</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>47300</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>54600</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>46400</v>
       </c>
       <c r="N8" t="n">
-        <v>4.89</v>
+        <v>14.15</v>
       </c>
       <c r="O8" t="n">
-        <v>207733000000</v>
+        <v>84677197325</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>108900</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급 계약 체결 및 정배열 가는 길에 따른 긍정적 전망.</t>
+          <t>하이퍼스케일러 수주, 1조 규모 수주, 연이은 1, 2차 수주 등 긍정적 공시와 뉴스가 언급되며 주가 상승 기대감을 높임. 유상증자 및 송전망 건설 이슈도 함께 논의됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성SDS 계약', '공급 계약', '정배열']</t>
+          <t>['수주', '공시', '유상증자']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,135 +1195,135 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14500</v>
+        <v>3625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.94%</t>
+          <t>'+6.62%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H9" t="n">
-        <v>10.75</v>
+        <v>0.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13310</v>
+        <v>3400</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3450</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4080</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3445</v>
       </c>
       <c r="N9" t="n">
-        <v>10.69</v>
+        <v>0.71</v>
       </c>
       <c r="O9" t="n">
-        <v>116185000000</v>
+        <v>147971486704</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['상승파동', '대장', '세력']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17460</v>
+        <v>31800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+8.72%</t>
+          <t>'+4.78%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.35</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G10" t="n">
-        <v>296</v>
+        <v>860</v>
       </c>
       <c r="H10" t="n">
-        <v>0.35</v>
+        <v>17.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16060</v>
+        <v>30350</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>30250</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>32300</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>30250</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>17.55</v>
       </c>
       <c r="O10" t="n">
-        <v>183008000000</v>
+        <v>13804643875</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등에 따른 동반 상승 기대, 세계 최초 타이틀 부각.</t>
+          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['양자보안', '세계최초', '보안주']</t>
+          <t>['FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,222 +1384,222 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4120</v>
+        <v>142600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.46%</t>
+          <t>'+4.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="H11" t="n">
-        <v>0.77</v>
+        <v>15.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3870</v>
+        <v>136700</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>139500</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>144100</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>138200</v>
       </c>
       <c r="N11" t="n">
-        <v>0.59</v>
+        <v>15.76</v>
       </c>
       <c r="O11" t="n">
-        <v>69169000000</v>
+        <v>109352661100</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>164700</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>87700</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
+          <t>합병 반대 목소리와 함께 정유 및 배터리 업황 호조 기대. 주가 급락 및 상승 가능성 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공급 계약', '광전자', '매물대']</t>
+          <t>['합병반대', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>14680</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'+4.04%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>47</v>
+      </c>
+      <c r="G12" t="n">
+        <v>193</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>14110</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14110</v>
+      </c>
+      <c r="L12" t="n">
         <v>15250</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>'+4.38%</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="E12" t="n">
-        <v>163</v>
-      </c>
-      <c r="F12" t="n">
-        <v>89</v>
-      </c>
-      <c r="G12" t="n">
-        <v>351</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>14610</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>13400</v>
       </c>
       <c r="N12" t="n">
-        <v>1.17</v>
+        <v>10.69</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>117417515155</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>23550</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-116000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['유가', '이란', '외인']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3655</v>
+        <v>14990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.98%</t>
+          <t>'+2.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.12</v>
+        <v>-1.17</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="G13" t="n">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="H13" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3515</v>
+        <v>14660</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>15460</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>14330</v>
       </c>
       <c r="N13" t="n">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="O13" t="n">
-        <v>146972000000</v>
+        <v>52816518190</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 주가 상승 기대감. 삼익제약과의 비교 및 대장주 언급.</t>
+          <t>유가 상승 및 이란 관련 뉴스 언급. 4배 상승 기대감과 함께 외인 유입 및 장난질 가능성 언급. 3~5% 상승 메리트 부족 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인매수', '주가상승', '대장주']</t>
+          <t>['유가', '이란', '외인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10180</v>
+        <v>19180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.67%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>123</v>
+        <v>387</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>10.53</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9820</v>
+        <v>18760</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>18440</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>19330</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>18120</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>10.55</v>
       </c>
       <c r="O14" t="n">
-        <v>154728000000</v>
+        <v>64917884320</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 의혹 제기, 투자자들의 불만 표출.</t>
+          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '신약']</t>
+          <t>['대차해지', '공시', '흐름']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14380</v>
+        <v>10430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.63%</t>
+          <t>'+1.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.08</v>
+        <v>0.26</v>
       </c>
       <c r="E15" t="n">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="G15" t="n">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8</v>
+        <v>17.93</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14150</v>
+        <v>10270</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>11650</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>10010</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>17.67</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>333811528985</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>22450</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>139000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 후 주가 회복 기대감, 15000원 및 16000원 돌파 전망. 120일선 15000원 지지선 언급.</t>
+          <t>아이온큐 급등과 트럼프 AI 정책 강화에 따른 광통신 대장주로서의 기대감. 기타법인 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '지지선', '회복']</t>
+          <t>['광통신', 'AI', '기타법인']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>226000</v>
+        <v>17460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.15</v>
+        <v>-2.35</v>
       </c>
       <c r="E16" t="n">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="G16" t="n">
-        <v>923</v>
+        <v>299</v>
       </c>
       <c r="H16" t="n">
-        <v>7.2</v>
+        <v>0.35</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>231000</v>
+        <v>17200</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>17220</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>18390</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="N16" t="n">
-        <v>7.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>184567949700</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-32000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
+          <t>미국 양자 보안주 폭등에 따른 동반 상승 기대, 세계 최초 타이틀 부각.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['패키징', '테라팹', '공매도']</t>
+          <t>['양자보안', '세계최초', '보안주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8690</v>
+        <v>10120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'+1.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>440</v>
+        <v>131</v>
       </c>
       <c r="H17" t="n">
-        <v>27.16</v>
+        <v>0.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8900</v>
+        <v>9990</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>10110</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>11390</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>9980</v>
       </c>
       <c r="N17" t="n">
-        <v>27.16</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>20271000000</v>
+        <v>155435993725</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>15960</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>부진한 실적과 낮은 목표주가에 대한 불만 제기. PBR 기준 저평가 논의.</t>
+          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['적자', '목표주가', 'PBR']</t>
+          <t>['주가조작', '저질약품']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20850</v>
+        <v>6920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.57%</t>
+          <t>'+0.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.09</v>
+        <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>208</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>492</v>
+        <v>131</v>
       </c>
       <c r="H18" t="n">
-        <v>28.9</v>
+        <v>0.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>21400</v>
+        <v>6900</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>8190</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6730</v>
       </c>
       <c r="N18" t="n">
-        <v>28.81</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>65866000000</v>
+        <v>44416542925</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>10360</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2965</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 불구하고 주가 하락. 시장이 수주를 악재로 인식하는 현상 발생.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['수주', '공시', '조선']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,43 +2115,43 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32500</v>
+        <v>1693500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-0.21%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>479</v>
       </c>
       <c r="G19" t="n">
-        <v>297</v>
+        <v>1713</v>
       </c>
       <c r="H19" t="n">
-        <v>14.93</v>
+        <v>50.27</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33600</v>
+        <v>1697000</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1690000</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1729000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1685000</v>
       </c>
       <c r="N19" t="n">
-        <v>15.06</v>
+        <v>50.47</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3126711243000</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-232000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-67000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한국거래소의 저평가 기업 PBR 딱지 부착 예고에 따른 기대감. 정배열 및 120일선 돌파.</t>
+          <t>AI 관련 긍정적 이슈와 기관 매수세 유입 기대. 금리 및 여러 변수에 대한 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['PBR', '저평가', '정배열']</t>
+          <t>['AI', '기관매수', '금리']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30250</v>
+        <v>248250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>166</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>107</v>
+        <v>496</v>
       </c>
       <c r="G20" t="n">
-        <v>849</v>
+        <v>1554</v>
       </c>
       <c r="H20" t="n">
-        <v>17.5</v>
+        <v>46.57</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>31450</v>
+        <v>249000</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>248000</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>252000</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>247500</v>
       </c>
       <c r="N20" t="n">
-        <v>17.55</v>
+        <v>46.64</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1841724657250</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-252000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-480000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 속 개인 투자자 혼조세. 부정적 전망과 긍정적 기대가 공존하며 혼조세.</t>
+          <t>시장 안정화 기대와 함께 일부 부정적 이슈 언급. 금리 인상 선반영 및 특별배당 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암']</t>
+          <t>['시장안정', '특별배당', '금리인상']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19000</v>
+        <v>223500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.47%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G21" t="n">
-        <v>373</v>
+        <v>934</v>
       </c>
       <c r="H21" t="n">
-        <v>10.53</v>
+        <v>7.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19890</v>
+        <v>225000</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>228500</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>229000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>219500</v>
       </c>
       <c r="N21" t="n">
-        <v>10.55</v>
+        <v>7.05</v>
       </c>
       <c r="O21" t="n">
-        <v>62464000000</v>
+        <v>87979219000</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>89500</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-128000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>머스크의 테라팹에 패키징 장비 공급 단독 보도. 공매도 세력과의 갈등 양상.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['패키징', '테라팹', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>247500</v>
+        <v>8710</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-1.58%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>118</v>
       </c>
       <c r="F22" t="n">
-        <v>492</v>
+        <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>1557</v>
+        <v>443</v>
       </c>
       <c r="H22" t="n">
-        <v>46.57</v>
+        <v>27.16</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>259500</v>
+        <v>8850</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>8750</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>8840</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>8670</v>
       </c>
       <c r="N22" t="n">
-        <v>46.64</v>
+        <v>27.16</v>
       </c>
       <c r="O22" t="n">
-        <v>1753772000000</v>
+        <v>20906905960</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-351000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>시장 안정화 기대 속에서 금리 인상 선반영 논의. 차트 기술적 분석 언급.</t>
+          <t>실적 부진 및 대표 사퇴 요구 등 부정적 여론 형성. 목표주가 하향 조정 및 적자 지속 우려.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['시장', '금리인상', '차트']</t>
+          <t>['실적부진', '목표주가', '적자']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>46400</v>
+        <v>14190</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="E23" t="n">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
-        <v>561</v>
+        <v>486</v>
       </c>
       <c r="H23" t="n">
-        <v>13.97</v>
+        <v>1.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>48800</v>
+        <v>14490</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>14410</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>13930</v>
       </c>
       <c r="N23" t="n">
-        <v>14.15</v>
+        <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>57884530595</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>하이퍼스케일러 및 3000억대 추가 수주 공시 확인, 20만 및 15만원 목표 주가 제시. 공매도 파산 가능성 및 적정가 35만원 언급.</t>
+          <t>언론 홍보 효과 및 지지 구간 언급. AI, 광전자 관련 테마주로 긍정적 전망.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수주 공시', '하이퍼스케일러', '적정가']</t>
+          <t>['언론홍보', '광통신', 'AI']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>85600</v>
+        <v>85100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.73%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.11</v>
       </c>
       <c r="E24" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G24" t="n">
-        <v>815</v>
+        <v>853</v>
       </c>
       <c r="H24" t="n">
         <v>23.45</v>
@@ -2619,34 +2619,34 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>90800</v>
+        <v>87000</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>86200</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>86800</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="N24" t="n">
         <v>23.56</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>111152932450</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-153000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-121000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2679,123 +2679,123 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1693000</v>
+        <v>4115</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-6.57%</t>
+          <t>'-4.86%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E25" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F25" t="n">
-        <v>480</v>
+        <v>44</v>
       </c>
       <c r="G25" t="n">
-        <v>1735</v>
+        <v>164</v>
       </c>
       <c r="H25" t="n">
-        <v>50.27</v>
+        <v>0.77</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1812000</v>
+        <v>4325</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4325</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4415</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4050</v>
       </c>
       <c r="N25" t="n">
-        <v>50.47</v>
+        <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>3036938000000</v>
+        <v>69809237756</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>-112000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>AI 관련 기술 발전 속도와 금리 인상 영향에 대한 논의. 기관 매수세 유입 확인.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['AI', '금리', '기관']</t>
+          <t>['공급 계약', '광전자', '매물대']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>133900</v>
+        <v>20850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-7.53%</t>
+          <t>'-5.66%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="F26" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="G26" t="n">
-        <v>319</v>
+        <v>499</v>
       </c>
       <c r="H26" t="n">
-        <v>15.81</v>
+        <v>28.9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,51 +2803,51 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>144800</v>
+        <v>22100</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>21850</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>21850</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="N26" t="n">
-        <v>15.76</v>
+        <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>66301417475</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>35350</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>18440</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>-1538000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-65000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>SK이노베이션 주주들은 합병 반대를 촉구하며, 회사 경영진에 대한 불만을 표출하고 있다. 주가 하락 및 변동성에 대한 우려가 나타나고 있으나, 정유주 슈퍼 사이클에 대한 기대도 일부 존재한다.</t>
+          <t>12억 달러 수주 공시에도 불구하고 주가 하락. 시장이 수주를 악재로 인식하는 현상 발생.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['합병 반대', '주가 하락', '정유주']</t>
+          <t>['수주', '공시', '조선']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
